--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_software_system_application.xlsx
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1525,22 +1525,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1095737459852965</v>
+        <v>0.1093335616203332</v>
       </c>
       <c r="C2">
-        <v>1973.996697310846</v>
+        <v>1961.662897303384</v>
       </c>
       <c r="D2">
-        <v>1970.726697310846</v>
+        <v>1978.176897303384</v>
       </c>
       <c r="E2">
-        <v>-19.1</v>
+        <v>0.6839999999999975</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.784</v>
       </c>
       <c r="G2">
         <v>3.27</v>
@@ -1561,28 +1561,28 @@
         <v>110.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9951351999999999</v>
       </c>
       <c r="N2">
-        <v>110.2</v>
+        <v>109.2048648</v>
       </c>
       <c r="O2">
-        <v>27.55</v>
+        <v>27.3012162</v>
       </c>
       <c r="P2">
-        <v>82.65000000000001</v>
+        <v>81.90364860000001</v>
       </c>
       <c r="Q2">
-        <v>90.35000000000001</v>
+        <v>89.60364860000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1095737459852965</v>
+        <v>0.110056880424579</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.287943062427952</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>110.7387217334891</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1093335616203332</v>
+        <v>0.10909337725537</v>
       </c>
       <c r="C3">
-        <v>1961.662897303384</v>
+        <v>1949.385641017607</v>
       </c>
       <c r="D3">
-        <v>1978.176897303384</v>
+        <v>1985.683641017607</v>
       </c>
       <c r="E3">
-        <v>0.6839999999999975</v>
+        <v>20.468</v>
       </c>
       <c r="F3">
-        <v>19.784</v>
+        <v>39.568</v>
       </c>
       <c r="G3">
         <v>3.27</v>
@@ -1643,28 +1643,28 @@
         <v>110.2</v>
       </c>
       <c r="M3">
-        <v>0.9951351999999999</v>
+        <v>1.9902704</v>
       </c>
       <c r="N3">
-        <v>109.2048648</v>
+        <v>108.2097296</v>
       </c>
       <c r="O3">
-        <v>27.3012162</v>
+        <v>27.0524324</v>
       </c>
       <c r="P3">
-        <v>81.90364860000001</v>
+        <v>81.1572972</v>
       </c>
       <c r="Q3">
-        <v>89.60364860000001</v>
+        <v>88.8572972</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.110056880424579</v>
+        <v>0.1105498747503775</v>
       </c>
       <c r="T3">
-        <v>1.287943062427952</v>
+        <v>1.297824473064963</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.7387217334891</v>
+        <v>55.36936086674454</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.10909337725537</v>
+        <v>0.1088531928904067</v>
       </c>
       <c r="C4">
-        <v>1949.385641017607</v>
+        <v>1937.165574618317</v>
       </c>
       <c r="D4">
-        <v>1985.683641017607</v>
+        <v>1993.247574618317</v>
       </c>
       <c r="E4">
-        <v>20.468</v>
+        <v>40.252</v>
       </c>
       <c r="F4">
-        <v>39.568</v>
+        <v>59.352</v>
       </c>
       <c r="G4">
         <v>3.27</v>
@@ -1725,28 +1725,28 @@
         <v>110.2</v>
       </c>
       <c r="M4">
-        <v>1.9902704</v>
+        <v>2.9854056</v>
       </c>
       <c r="N4">
-        <v>108.2097296</v>
+        <v>107.2145944</v>
       </c>
       <c r="O4">
-        <v>27.0524324</v>
+        <v>26.8036486</v>
       </c>
       <c r="P4">
-        <v>81.1572972</v>
+        <v>80.41094580000001</v>
       </c>
       <c r="Q4">
-        <v>88.8572972</v>
+        <v>88.11094580000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1105498747503775</v>
+        <v>0.1110530339076358</v>
       </c>
       <c r="T4">
-        <v>1.297824473064963</v>
+        <v>1.307909624127479</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.36936086674454</v>
+        <v>36.91290724449637</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1088531928904067</v>
+        <v>0.1086130085254435</v>
       </c>
       <c r="C5">
-        <v>1937.165574618317</v>
+        <v>1925.003354153527</v>
       </c>
       <c r="D5">
-        <v>1993.247574618317</v>
+        <v>2000.869354153527</v>
       </c>
       <c r="E5">
-        <v>40.252</v>
+        <v>60.03599999999999</v>
       </c>
       <c r="F5">
-        <v>59.352</v>
+        <v>79.136</v>
       </c>
       <c r="G5">
         <v>3.27</v>
@@ -1807,28 +1807,28 @@
         <v>110.2</v>
       </c>
       <c r="M5">
-        <v>2.9854056</v>
+        <v>3.9805408</v>
       </c>
       <c r="N5">
-        <v>107.2145944</v>
+        <v>106.2194592</v>
       </c>
       <c r="O5">
-        <v>26.8036486</v>
+        <v>26.5548648</v>
       </c>
       <c r="P5">
-        <v>80.41094580000001</v>
+        <v>79.6645944</v>
       </c>
       <c r="Q5">
-        <v>88.11094580000001</v>
+        <v>87.3645944</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1110530339076358</v>
+        <v>0.111566675547337</v>
       </c>
       <c r="T5">
-        <v>1.307909624127479</v>
+        <v>1.318204882503797</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.91290724449637</v>
+        <v>27.68468043337227</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1086130085254435</v>
+        <v>0.1083728241604803</v>
       </c>
       <c r="C6">
-        <v>1925.003354153527</v>
+        <v>1912.899645744158</v>
       </c>
       <c r="D6">
-        <v>2000.869354153527</v>
+        <v>2008.549645744158</v>
       </c>
       <c r="E6">
-        <v>60.03599999999999</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="F6">
-        <v>79.136</v>
+        <v>98.92</v>
       </c>
       <c r="G6">
         <v>3.27</v>
@@ -1889,28 +1889,28 @@
         <v>110.2</v>
       </c>
       <c r="M6">
-        <v>3.9805408</v>
+        <v>4.975676</v>
       </c>
       <c r="N6">
-        <v>106.2194592</v>
+        <v>105.224324</v>
       </c>
       <c r="O6">
-        <v>26.5548648</v>
+        <v>26.306081</v>
       </c>
       <c r="P6">
-        <v>79.6645944</v>
+        <v>78.91824299999999</v>
       </c>
       <c r="Q6">
-        <v>87.3645944</v>
+        <v>86.61824299999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.111566675547337</v>
+        <v>0.1120911306952424</v>
       </c>
       <c r="T6">
-        <v>1.318204882503797</v>
+        <v>1.328716883161722</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.68468043337227</v>
+        <v>22.14774434669781</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1083728241604803</v>
+        <v>0.108132639795517</v>
       </c>
       <c r="C7">
-        <v>1912.899645744158</v>
+        <v>1900.855125778098</v>
       </c>
       <c r="D7">
-        <v>2008.549645744158</v>
+        <v>2016.289125778098</v>
       </c>
       <c r="E7">
-        <v>79.81999999999999</v>
+        <v>99.60400000000001</v>
       </c>
       <c r="F7">
-        <v>98.92</v>
+        <v>118.704</v>
       </c>
       <c r="G7">
         <v>3.27</v>
@@ -1971,28 +1971,28 @@
         <v>110.2</v>
       </c>
       <c r="M7">
-        <v>4.975676</v>
+        <v>5.9708112</v>
       </c>
       <c r="N7">
-        <v>105.224324</v>
+        <v>104.2291888</v>
       </c>
       <c r="O7">
-        <v>26.306081</v>
+        <v>26.0572972</v>
       </c>
       <c r="P7">
-        <v>78.91824299999999</v>
+        <v>78.17189160000001</v>
       </c>
       <c r="Q7">
-        <v>86.61824299999999</v>
+        <v>85.87189160000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1120911306952424</v>
+        <v>0.112626744463316</v>
       </c>
       <c r="T7">
-        <v>1.328716883161722</v>
+        <v>1.339452543408113</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.14774434669781</v>
+        <v>18.45645362224818</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.108132639795517</v>
+        <v>0.1078924554305538</v>
       </c>
       <c r="C8">
-        <v>1900.855125778098</v>
+        <v>1888.870481108779</v>
       </c>
       <c r="D8">
-        <v>2016.289125778098</v>
+        <v>2024.088481108779</v>
       </c>
       <c r="E8">
-        <v>99.60399999999998</v>
+        <v>119.388</v>
       </c>
       <c r="F8">
-        <v>118.704</v>
+        <v>138.488</v>
       </c>
       <c r="G8">
         <v>3.27</v>
@@ -2053,28 +2053,28 @@
         <v>110.2</v>
       </c>
       <c r="M8">
-        <v>5.970811199999999</v>
+        <v>6.965946399999998</v>
       </c>
       <c r="N8">
-        <v>104.2291888</v>
+        <v>103.2340536</v>
       </c>
       <c r="O8">
-        <v>26.0572972</v>
+        <v>25.8085134</v>
       </c>
       <c r="P8">
-        <v>78.17189160000001</v>
+        <v>77.4255402</v>
       </c>
       <c r="Q8">
-        <v>85.87189160000001</v>
+        <v>85.1255402</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.112626744463316</v>
+        <v>0.113173876807047</v>
       </c>
       <c r="T8">
-        <v>1.339452543408113</v>
+        <v>1.350419078068406</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.45645362224818</v>
+        <v>15.81981739049844</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2099,22 +2099,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1078924554305537</v>
+        <v>0.1076522710655905</v>
       </c>
       <c r="C9">
-        <v>1888.870481108779</v>
+        <v>1876.946409258369</v>
       </c>
       <c r="D9">
-        <v>2024.088481108779</v>
+        <v>2031.948409258369</v>
       </c>
       <c r="E9">
-        <v>119.388</v>
+        <v>139.172</v>
       </c>
       <c r="F9">
-        <v>138.488</v>
+        <v>158.272</v>
       </c>
       <c r="G9">
         <v>3.27</v>
@@ -2135,28 +2135,28 @@
         <v>110.2</v>
       </c>
       <c r="M9">
-        <v>6.9659464</v>
+        <v>7.961081599999999</v>
       </c>
       <c r="N9">
-        <v>103.2340536</v>
+        <v>102.2389184</v>
       </c>
       <c r="O9">
-        <v>25.8085134</v>
+        <v>25.5597296</v>
       </c>
       <c r="P9">
-        <v>77.4255402</v>
+        <v>76.67918880000001</v>
       </c>
       <c r="Q9">
-        <v>85.1255402</v>
+        <v>84.37918880000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.113173876807047</v>
+        <v>0.1137329033321636</v>
       </c>
       <c r="T9">
-        <v>1.350419078068406</v>
+        <v>1.361624015656096</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.81981739049844</v>
+        <v>13.84234021668614</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1076522710655905</v>
+        <v>0.1075133367006273</v>
       </c>
       <c r="C10">
-        <v>1876.946409258369</v>
+        <v>1861.73690606848</v>
       </c>
       <c r="D10">
-        <v>2031.948409258369</v>
+        <v>2036.52290606848</v>
       </c>
       <c r="E10">
-        <v>139.172</v>
+        <v>158.956</v>
       </c>
       <c r="F10">
-        <v>158.272</v>
+        <v>178.056</v>
       </c>
       <c r="G10">
         <v>3.27</v>
@@ -2217,45 +2217,45 @@
         <v>110.2</v>
       </c>
       <c r="M10">
-        <v>7.961081599999999</v>
+        <v>9.223300799999999</v>
       </c>
       <c r="N10">
-        <v>102.2389184</v>
+        <v>100.9766992</v>
       </c>
       <c r="O10">
-        <v>25.5597296</v>
+        <v>25.2441748</v>
       </c>
       <c r="P10">
-        <v>76.67918880000001</v>
+        <v>75.7325244</v>
       </c>
       <c r="Q10">
-        <v>84.37918880000001</v>
+        <v>83.43252440000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1137329033321636</v>
+        <v>0.1143042161545355</v>
       </c>
       <c r="T10">
-        <v>1.361624015656096</v>
+        <v>1.373075215608351</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.84234021668614</v>
+        <v>11.94800022135243</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1075133367006273</v>
+        <v>0.107284402335664</v>
       </c>
       <c r="C11">
-        <v>1861.73690606848</v>
+        <v>1849.53580612968</v>
       </c>
       <c r="D11">
-        <v>2036.52290606848</v>
+        <v>2044.10580612968</v>
       </c>
       <c r="E11">
-        <v>158.956</v>
+        <v>178.74</v>
       </c>
       <c r="F11">
-        <v>178.056</v>
+        <v>197.84</v>
       </c>
       <c r="G11">
         <v>3.27</v>
@@ -2299,28 +2299,28 @@
         <v>110.2</v>
       </c>
       <c r="M11">
-        <v>9.223300799999999</v>
+        <v>10.248112</v>
       </c>
       <c r="N11">
-        <v>100.9766992</v>
+        <v>99.951888</v>
       </c>
       <c r="O11">
-        <v>25.2441748</v>
+        <v>24.987972</v>
       </c>
       <c r="P11">
-        <v>75.7325244</v>
+        <v>74.963916</v>
       </c>
       <c r="Q11">
-        <v>83.43252440000001</v>
+        <v>82.663916</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1143042161545355</v>
+        <v>0.1148882248174045</v>
       </c>
       <c r="T11">
-        <v>1.373075215608351</v>
+        <v>1.384780886670655</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.94800022135243</v>
+        <v>10.75320019921718</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2345,22 +2345,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.107284402335664</v>
+        <v>0.1071957179707008</v>
       </c>
       <c r="C12">
-        <v>1849.53580612968</v>
+        <v>1832.704458714031</v>
       </c>
       <c r="D12">
-        <v>2044.10580612968</v>
+        <v>2047.058458714031</v>
       </c>
       <c r="E12">
-        <v>178.74</v>
+        <v>198.524</v>
       </c>
       <c r="F12">
-        <v>197.84</v>
+        <v>217.624</v>
       </c>
       <c r="G12">
         <v>3.27</v>
@@ -2381,45 +2381,45 @@
         <v>110.2</v>
       </c>
       <c r="M12">
-        <v>10.248112</v>
+        <v>11.642884</v>
       </c>
       <c r="N12">
-        <v>99.951888</v>
+        <v>98.55711600000001</v>
       </c>
       <c r="O12">
-        <v>24.987972</v>
+        <v>24.639279</v>
       </c>
       <c r="P12">
-        <v>74.963916</v>
+        <v>73.91783700000001</v>
       </c>
       <c r="Q12">
-        <v>82.663916</v>
+        <v>81.61783700000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1148882248174045</v>
+        <v>0.1154853572704503</v>
       </c>
       <c r="T12">
-        <v>1.384780886670655</v>
+        <v>1.396749606520877</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.75320019921718</v>
+        <v>9.465008841451999</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2427,22 +2427,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1071957179707008</v>
+        <v>0.1069795336057376</v>
       </c>
       <c r="C13">
-        <v>1832.704458714031</v>
+        <v>1820.153956697059</v>
       </c>
       <c r="D13">
-        <v>2047.058458714031</v>
+        <v>2054.291956697059</v>
       </c>
       <c r="E13">
-        <v>198.524</v>
+        <v>218.308</v>
       </c>
       <c r="F13">
-        <v>217.624</v>
+        <v>237.408</v>
       </c>
       <c r="G13">
         <v>3.27</v>
@@ -2463,28 +2463,28 @@
         <v>110.2</v>
       </c>
       <c r="M13">
-        <v>11.642884</v>
+        <v>12.701328</v>
       </c>
       <c r="N13">
-        <v>98.55711600000001</v>
+        <v>97.498672</v>
       </c>
       <c r="O13">
-        <v>24.639279</v>
+        <v>24.374668</v>
       </c>
       <c r="P13">
-        <v>73.91783700000001</v>
+        <v>73.124004</v>
       </c>
       <c r="Q13">
-        <v>81.61783700000001</v>
+        <v>80.824004</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1154853572704503</v>
+        <v>0.1160960609156109</v>
       </c>
       <c r="T13">
-        <v>1.396749606520877</v>
+        <v>1.408990342731331</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.465008841451999</v>
+        <v>8.676258104664331</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1069795336057376</v>
+        <v>0.1067633492407743</v>
       </c>
       <c r="C14">
-        <v>1820.153956697059</v>
+        <v>1807.654756624203</v>
       </c>
       <c r="D14">
-        <v>2054.291956697059</v>
+        <v>2061.576756624203</v>
       </c>
       <c r="E14">
-        <v>218.308</v>
+        <v>238.092</v>
       </c>
       <c r="F14">
-        <v>237.408</v>
+        <v>257.192</v>
       </c>
       <c r="G14">
         <v>3.27</v>
@@ -2545,28 +2545,28 @@
         <v>110.2</v>
       </c>
       <c r="M14">
-        <v>12.701328</v>
+        <v>13.759772</v>
       </c>
       <c r="N14">
-        <v>97.498672</v>
+        <v>96.440228</v>
       </c>
       <c r="O14">
-        <v>24.374668</v>
+        <v>24.110057</v>
       </c>
       <c r="P14">
-        <v>73.124004</v>
+        <v>72.33017100000001</v>
       </c>
       <c r="Q14">
-        <v>80.824004</v>
+        <v>80.03017100000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1160960609156109</v>
+        <v>0.1167208037250279</v>
       </c>
       <c r="T14">
-        <v>1.408990342731331</v>
+        <v>1.421512475176508</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.676258104664331</v>
+        <v>8.008853635074768</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2591,22 +2591,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1067633492407743</v>
+        <v>0.1066311648758111</v>
       </c>
       <c r="C15">
-        <v>1807.654756624203</v>
+        <v>1792.35050339469</v>
       </c>
       <c r="D15">
-        <v>2061.576756624203</v>
+        <v>2066.05650339469</v>
       </c>
       <c r="E15">
-        <v>238.092</v>
+        <v>257.876</v>
       </c>
       <c r="F15">
-        <v>257.192</v>
+        <v>276.976</v>
       </c>
       <c r="G15">
         <v>3.27</v>
@@ -2627,45 +2627,45 @@
         <v>110.2</v>
       </c>
       <c r="M15">
-        <v>13.759772</v>
+        <v>15.0397968</v>
       </c>
       <c r="N15">
-        <v>96.440228</v>
+        <v>95.1602032</v>
       </c>
       <c r="O15">
-        <v>24.110057</v>
+        <v>23.7900508</v>
       </c>
       <c r="P15">
-        <v>72.33017100000001</v>
+        <v>71.37015239999999</v>
       </c>
       <c r="Q15">
-        <v>80.03017100000001</v>
+        <v>79.0701524</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1167208037250279</v>
+        <v>0.1173600754369896</v>
       </c>
       <c r="T15">
-        <v>1.421512475176508</v>
+        <v>1.434325820004131</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.008853635074768</v>
+        <v>7.327226655083532</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2673,22 +2673,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1066311648758111</v>
+        <v>0.1064209805108478</v>
       </c>
       <c r="C16">
-        <v>1792.35050339469</v>
+        <v>1779.729910691715</v>
       </c>
       <c r="D16">
-        <v>2066.05650339469</v>
+        <v>2073.219910691715</v>
       </c>
       <c r="E16">
-        <v>257.876</v>
+        <v>277.66</v>
       </c>
       <c r="F16">
-        <v>276.976</v>
+        <v>296.76</v>
       </c>
       <c r="G16">
         <v>3.27</v>
@@ -2709,28 +2709,28 @@
         <v>110.2</v>
       </c>
       <c r="M16">
-        <v>15.0397968</v>
+        <v>16.114068</v>
       </c>
       <c r="N16">
-        <v>95.1602032</v>
+        <v>94.085932</v>
       </c>
       <c r="O16">
-        <v>23.7900508</v>
+        <v>23.521483</v>
       </c>
       <c r="P16">
-        <v>71.37015239999999</v>
+        <v>70.564449</v>
       </c>
       <c r="Q16">
-        <v>79.0701524</v>
+        <v>78.264449</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1173600754369896</v>
+        <v>0.1180143888362916</v>
       </c>
       <c r="T16">
-        <v>1.434325820004131</v>
+        <v>1.447440655298287</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.327226655083532</v>
+        <v>6.838744878077962</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2755,22 +2755,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1064209805108478</v>
+        <v>0.1062107961458846</v>
       </c>
       <c r="C17">
-        <v>1779.729910691715</v>
+        <v>1767.159164582718</v>
       </c>
       <c r="D17">
-        <v>2073.219910691715</v>
+        <v>2080.433164582718</v>
       </c>
       <c r="E17">
-        <v>277.66</v>
+        <v>297.444</v>
       </c>
       <c r="F17">
-        <v>296.76</v>
+        <v>316.544</v>
       </c>
       <c r="G17">
         <v>3.27</v>
@@ -2791,28 +2791,28 @@
         <v>110.2</v>
       </c>
       <c r="M17">
-        <v>16.114068</v>
+        <v>17.1883392</v>
       </c>
       <c r="N17">
-        <v>94.085932</v>
+        <v>93.0116608</v>
       </c>
       <c r="O17">
-        <v>23.521483</v>
+        <v>23.2529152</v>
       </c>
       <c r="P17">
-        <v>70.564449</v>
+        <v>69.7587456</v>
       </c>
       <c r="Q17">
-        <v>78.264449</v>
+        <v>77.4587456</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1180143888362916</v>
+        <v>0.1186842811260531</v>
       </c>
       <c r="T17">
-        <v>1.447440655298287</v>
+        <v>1.460867748575636</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.838744878077962</v>
+        <v>6.411323323198091</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2837,22 +2837,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1062107961458846</v>
+        <v>0.1061281117809214</v>
       </c>
       <c r="C18">
-        <v>1767.159164582718</v>
+        <v>1750.226559893856</v>
       </c>
       <c r="D18">
-        <v>2080.433164582718</v>
+        <v>2083.284559893856</v>
       </c>
       <c r="E18">
-        <v>297.444</v>
+        <v>317.228</v>
       </c>
       <c r="F18">
-        <v>316.544</v>
+        <v>336.328</v>
       </c>
       <c r="G18">
         <v>3.27</v>
@@ -2873,45 +2873,45 @@
         <v>110.2</v>
       </c>
       <c r="M18">
-        <v>17.1883392</v>
+        <v>18.5989384</v>
       </c>
       <c r="N18">
-        <v>93.0116608</v>
+        <v>91.60106160000001</v>
       </c>
       <c r="O18">
-        <v>23.2529152</v>
+        <v>22.9002654</v>
       </c>
       <c r="P18">
-        <v>69.7587456</v>
+        <v>68.70079620000001</v>
       </c>
       <c r="Q18">
-        <v>77.4587456</v>
+        <v>76.40079620000002</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1186842811260531</v>
+        <v>0.1193703153987004</v>
       </c>
       <c r="T18">
-        <v>1.460867748575636</v>
+        <v>1.474618386269308</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.411323323198091</v>
+        <v>5.925069357722053</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2919,22 +2919,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1061281117809214</v>
+        <v>0.1059254274159581</v>
       </c>
       <c r="C19">
-        <v>1750.226559893856</v>
+        <v>1737.465365821516</v>
       </c>
       <c r="D19">
-        <v>2083.284559893856</v>
+        <v>2090.307365821516</v>
       </c>
       <c r="E19">
-        <v>317.228</v>
+        <v>337.012</v>
       </c>
       <c r="F19">
-        <v>336.328</v>
+        <v>356.112</v>
       </c>
       <c r="G19">
         <v>3.27</v>
@@ -2955,28 +2955,28 @@
         <v>110.2</v>
       </c>
       <c r="M19">
-        <v>18.5989384</v>
+        <v>19.6929936</v>
       </c>
       <c r="N19">
-        <v>91.60106160000001</v>
+        <v>90.50700639999999</v>
       </c>
       <c r="O19">
-        <v>22.9002654</v>
+        <v>22.6267516</v>
       </c>
       <c r="P19">
-        <v>68.70079620000001</v>
+        <v>67.88025479999999</v>
       </c>
       <c r="Q19">
-        <v>76.40079620000002</v>
+        <v>75.58025479999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1193703153987004</v>
+        <v>0.120073082214583</v>
       </c>
       <c r="T19">
-        <v>1.474618386269308</v>
+        <v>1.488704405370141</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.925069357722053</v>
+        <v>5.595898837848604</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3001,22 +3001,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1059254274159581</v>
+        <v>0.1057227430509949</v>
       </c>
       <c r="C20">
-        <v>1737.465365821515</v>
+        <v>1724.751680020232</v>
       </c>
       <c r="D20">
-        <v>2090.307365821515</v>
+        <v>2097.377680020232</v>
       </c>
       <c r="E20">
-        <v>337.0119999999999</v>
+        <v>356.7959999999999</v>
       </c>
       <c r="F20">
-        <v>356.112</v>
+        <v>375.896</v>
       </c>
       <c r="G20">
         <v>3.27</v>
@@ -3037,28 +3037,28 @@
         <v>110.2</v>
       </c>
       <c r="M20">
-        <v>19.6929936</v>
+        <v>20.7870488</v>
       </c>
       <c r="N20">
-        <v>90.50700640000001</v>
+        <v>89.41295120000001</v>
       </c>
       <c r="O20">
-        <v>22.6267516</v>
+        <v>22.3532378</v>
       </c>
       <c r="P20">
-        <v>67.8802548</v>
+        <v>67.05971340000001</v>
       </c>
       <c r="Q20">
-        <v>75.58025480000001</v>
+        <v>74.75971340000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.120073082214583</v>
+        <v>0.1207932012975245</v>
       </c>
       <c r="T20">
-        <v>1.488704405370141</v>
+        <v>1.503138227411737</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.595898837848605</v>
+        <v>5.30137784638289</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1057227430509949</v>
+        <v>0.1055200586860316</v>
       </c>
       <c r="C21">
-        <v>1724.751680020232</v>
+        <v>1712.085986206063</v>
       </c>
       <c r="D21">
-        <v>2097.377680020232</v>
+        <v>2104.495986206063</v>
       </c>
       <c r="E21">
-        <v>356.7959999999999</v>
+        <v>376.58</v>
       </c>
       <c r="F21">
-        <v>375.896</v>
+        <v>395.68</v>
       </c>
       <c r="G21">
         <v>3.27</v>
@@ -3119,28 +3119,28 @@
         <v>110.2</v>
       </c>
       <c r="M21">
-        <v>20.7870488</v>
+        <v>21.881104</v>
       </c>
       <c r="N21">
-        <v>89.41295120000001</v>
+        <v>88.318896</v>
       </c>
       <c r="O21">
-        <v>22.3532378</v>
+        <v>22.079724</v>
       </c>
       <c r="P21">
-        <v>67.05971340000001</v>
+        <v>66.239172</v>
       </c>
       <c r="Q21">
-        <v>74.75971340000001</v>
+        <v>73.939172</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1207932012975245</v>
+        <v>0.1215313233575395</v>
       </c>
       <c r="T21">
-        <v>1.503138227411737</v>
+        <v>1.517932895004372</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.30137784638289</v>
+        <v>5.036308954063744</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3165,22 +3165,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1055200586860316</v>
+        <v>0.1053173743210684</v>
       </c>
       <c r="C22">
-        <v>1712.085986206063</v>
+        <v>1699.468774684177</v>
       </c>
       <c r="D22">
-        <v>2104.495986206063</v>
+        <v>2111.662774684177</v>
       </c>
       <c r="E22">
-        <v>376.58</v>
+        <v>396.364</v>
       </c>
       <c r="F22">
-        <v>395.68</v>
+        <v>415.464</v>
       </c>
       <c r="G22">
         <v>3.27</v>
@@ -3201,28 +3201,28 @@
         <v>110.2</v>
       </c>
       <c r="M22">
-        <v>21.881104</v>
+        <v>22.9751592</v>
       </c>
       <c r="N22">
-        <v>88.318896</v>
+        <v>87.22484080000001</v>
       </c>
       <c r="O22">
-        <v>22.079724</v>
+        <v>21.8062102</v>
       </c>
       <c r="P22">
-        <v>66.239172</v>
+        <v>65.4186306</v>
       </c>
       <c r="Q22">
-        <v>73.939172</v>
+        <v>73.1186306</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1215313233575395</v>
+        <v>0.1222881320519853</v>
       </c>
       <c r="T22">
-        <v>1.517932895004372</v>
+        <v>1.533102111143656</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.036308954063744</v>
+        <v>4.796484718155947</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3247,22 +3247,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1053173743210684</v>
+        <v>0.1051146899561051</v>
       </c>
       <c r="C23">
-        <v>1699.468774684177</v>
+        <v>1686.900542461437</v>
       </c>
       <c r="D23">
-        <v>2111.662774684177</v>
+        <v>2118.878542461437</v>
       </c>
       <c r="E23">
-        <v>396.3639999999999</v>
+        <v>416.148</v>
       </c>
       <c r="F23">
-        <v>415.4639999999999</v>
+        <v>435.248</v>
       </c>
       <c r="G23">
         <v>3.27</v>
@@ -3283,28 +3283,28 @@
         <v>110.2</v>
       </c>
       <c r="M23">
-        <v>22.9751592</v>
+        <v>24.0692144</v>
       </c>
       <c r="N23">
-        <v>87.22484080000001</v>
+        <v>86.1307856</v>
       </c>
       <c r="O23">
-        <v>21.8062102</v>
+        <v>21.5326964</v>
       </c>
       <c r="P23">
-        <v>65.4186306</v>
+        <v>64.5980892</v>
       </c>
       <c r="Q23">
-        <v>73.1186306</v>
+        <v>72.29808920000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1222881320519853</v>
+        <v>0.1230643460975707</v>
       </c>
       <c r="T23">
-        <v>1.533102111143656</v>
+        <v>1.548660281542922</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.796484718155948</v>
+        <v>4.578462685512495</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1051146899561051</v>
+        <v>0.1053432555911419</v>
       </c>
       <c r="C24">
-        <v>1686.900542461437</v>
+        <v>1658.982912299375</v>
       </c>
       <c r="D24">
-        <v>2118.878542461437</v>
+        <v>2110.744912299375</v>
       </c>
       <c r="E24">
-        <v>416.148</v>
+        <v>435.932</v>
       </c>
       <c r="F24">
-        <v>435.248</v>
+        <v>455.032</v>
       </c>
       <c r="G24">
         <v>3.27</v>
@@ -3365,45 +3365,45 @@
         <v>110.2</v>
       </c>
       <c r="M24">
-        <v>24.0692144</v>
+        <v>26.3008496</v>
       </c>
       <c r="N24">
-        <v>86.1307856</v>
+        <v>83.8991504</v>
       </c>
       <c r="O24">
-        <v>21.5326964</v>
+        <v>20.9747876</v>
       </c>
       <c r="P24">
-        <v>64.5980892</v>
+        <v>62.9243628</v>
       </c>
       <c r="Q24">
-        <v>72.29808920000001</v>
+        <v>70.6243628</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1230643460975707</v>
+        <v>0.1238607215469375</v>
       </c>
       <c r="T24">
-        <v>1.548660281542922</v>
+        <v>1.564622560264247</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.578462685512495</v>
+        <v>4.189978714603956</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3411,22 +3411,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1053432555911419</v>
+        <v>0.1051593212261787</v>
       </c>
       <c r="C25">
-        <v>1658.982912299375</v>
+        <v>1645.739393508112</v>
       </c>
       <c r="D25">
-        <v>2110.744912299375</v>
+        <v>2117.285393508112</v>
       </c>
       <c r="E25">
-        <v>435.932</v>
+        <v>455.716</v>
       </c>
       <c r="F25">
-        <v>455.032</v>
+        <v>474.816</v>
       </c>
       <c r="G25">
         <v>3.27</v>
@@ -3447,28 +3447,28 @@
         <v>110.2</v>
       </c>
       <c r="M25">
-        <v>26.3008496</v>
+        <v>27.4443648</v>
       </c>
       <c r="N25">
-        <v>83.8991504</v>
+        <v>82.7556352</v>
       </c>
       <c r="O25">
-        <v>20.9747876</v>
+        <v>20.6889088</v>
       </c>
       <c r="P25">
-        <v>62.9243628</v>
+        <v>62.0667264</v>
       </c>
       <c r="Q25">
-        <v>70.6243628</v>
+        <v>69.76672640000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1238607215469375</v>
+        <v>0.1246780542449719</v>
       </c>
       <c r="T25">
-        <v>1.564622560264247</v>
+        <v>1.581004898951922</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.189978714603956</v>
+        <v>4.015396268162125</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1051593212261787</v>
+        <v>0.1056316368612154</v>
       </c>
       <c r="C26">
-        <v>1645.739393508112</v>
+        <v>1609.241376515589</v>
       </c>
       <c r="D26">
-        <v>2117.285393508112</v>
+        <v>2100.571376515589</v>
       </c>
       <c r="E26">
-        <v>455.716</v>
+        <v>475.4999999999999</v>
       </c>
       <c r="F26">
-        <v>474.816</v>
+        <v>494.6</v>
       </c>
       <c r="G26">
         <v>3.27</v>
@@ -3529,45 +3529,45 @@
         <v>110.2</v>
       </c>
       <c r="M26">
-        <v>27.4443648</v>
+        <v>30.31898</v>
       </c>
       <c r="N26">
-        <v>82.7556352</v>
+        <v>79.88102000000001</v>
       </c>
       <c r="O26">
-        <v>20.6889088</v>
+        <v>19.970255</v>
       </c>
       <c r="P26">
-        <v>62.0667264</v>
+        <v>59.910765</v>
       </c>
       <c r="Q26">
-        <v>69.76672640000001</v>
+        <v>67.61076500000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1246780542449719</v>
+        <v>0.1255171824816206</v>
       </c>
       <c r="T26">
-        <v>1.581004898951922</v>
+        <v>1.597824100004602</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.015396268162126</v>
+        <v>3.634686918887113</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1056316368612154</v>
+        <v>0.1060199524962522</v>
       </c>
       <c r="C27">
-        <v>1609.241376515589</v>
+        <v>1575.912285989945</v>
       </c>
       <c r="D27">
-        <v>2100.571376515589</v>
+        <v>2087.026285989945</v>
       </c>
       <c r="E27">
-        <v>475.4999999999999</v>
+        <v>495.284</v>
       </c>
       <c r="F27">
-        <v>494.6</v>
+        <v>514.384</v>
       </c>
       <c r="G27">
         <v>3.27</v>
@@ -3611,45 +3611,45 @@
         <v>110.2</v>
       </c>
       <c r="M27">
-        <v>30.31898</v>
+        <v>32.97201440000001</v>
       </c>
       <c r="N27">
-        <v>79.88102000000001</v>
+        <v>77.2279856</v>
       </c>
       <c r="O27">
-        <v>19.970255</v>
+        <v>19.3069964</v>
       </c>
       <c r="P27">
-        <v>59.910765</v>
+        <v>57.92098919999999</v>
       </c>
       <c r="Q27">
-        <v>67.61076500000001</v>
+        <v>65.6209892</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1255171824816206</v>
+        <v>0.1263789898598003</v>
       </c>
       <c r="T27">
-        <v>1.597824100004602</v>
+        <v>1.615097874058706</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.634686918887113</v>
+        <v>3.342228311049142</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3657,22 +3657,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1060199524962522</v>
+        <v>0.1058832681312889</v>
       </c>
       <c r="C28">
-        <v>1575.912285989945</v>
+        <v>1560.876094680024</v>
       </c>
       <c r="D28">
-        <v>2087.026285989945</v>
+        <v>2091.774094680025</v>
       </c>
       <c r="E28">
-        <v>495.284</v>
+        <v>515.068</v>
       </c>
       <c r="F28">
-        <v>514.384</v>
+        <v>534.168</v>
       </c>
       <c r="G28">
         <v>3.27</v>
@@ -3693,28 +3693,28 @@
         <v>110.2</v>
       </c>
       <c r="M28">
-        <v>32.97201440000001</v>
+        <v>34.2401688</v>
       </c>
       <c r="N28">
-        <v>77.2279856</v>
+        <v>75.9598312</v>
       </c>
       <c r="O28">
-        <v>19.3069964</v>
+        <v>18.9899578</v>
       </c>
       <c r="P28">
-        <v>57.92098919999999</v>
+        <v>56.9698734</v>
       </c>
       <c r="Q28">
-        <v>65.6209892</v>
+        <v>64.6698734</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1263789898598003</v>
+        <v>0.1272644083990259</v>
       </c>
       <c r="T28">
-        <v>1.615097874058706</v>
+        <v>1.632844902196484</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.342228311049142</v>
+        <v>3.218442077306582</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1058832681312889</v>
+        <v>0.1057465837663257</v>
       </c>
       <c r="C29">
-        <v>1560.876094680024</v>
+        <v>1545.861554352529</v>
       </c>
       <c r="D29">
-        <v>2091.774094680025</v>
+        <v>2096.543554352529</v>
       </c>
       <c r="E29">
-        <v>515.068</v>
+        <v>534.852</v>
       </c>
       <c r="F29">
-        <v>534.168</v>
+        <v>553.952</v>
       </c>
       <c r="G29">
         <v>3.27</v>
@@ -3775,28 +3775,28 @@
         <v>110.2</v>
       </c>
       <c r="M29">
-        <v>34.2401688</v>
+        <v>35.5083232</v>
       </c>
       <c r="N29">
-        <v>75.9598312</v>
+        <v>74.69167680000001</v>
       </c>
       <c r="O29">
-        <v>18.9899578</v>
+        <v>18.6729192</v>
       </c>
       <c r="P29">
-        <v>56.9698734</v>
+        <v>56.01875760000001</v>
       </c>
       <c r="Q29">
-        <v>64.6698734</v>
+        <v>63.71875760000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1272644083990259</v>
+        <v>0.1281744218976746</v>
       </c>
       <c r="T29">
-        <v>1.632844902196484</v>
+        <v>1.651084903338089</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.218442077306582</v>
+        <v>3.103497717402775</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1057465837663257</v>
+        <v>0.1073063994013625</v>
       </c>
       <c r="C30">
-        <v>1545.861554352529</v>
+        <v>1472.908754887052</v>
       </c>
       <c r="D30">
-        <v>2096.543554352529</v>
+        <v>2043.374754887052</v>
       </c>
       <c r="E30">
-        <v>534.852</v>
+        <v>554.636</v>
       </c>
       <c r="F30">
-        <v>553.952</v>
+        <v>573.736</v>
       </c>
       <c r="G30">
         <v>3.27</v>
@@ -3857,45 +3857,45 @@
         <v>110.2</v>
       </c>
       <c r="M30">
-        <v>35.5083232</v>
+        <v>41.25161840000001</v>
       </c>
       <c r="N30">
-        <v>74.69167680000001</v>
+        <v>68.9483816</v>
       </c>
       <c r="O30">
-        <v>18.6729192</v>
+        <v>17.2370954</v>
       </c>
       <c r="P30">
-        <v>56.01875760000001</v>
+        <v>51.7112862</v>
       </c>
       <c r="Q30">
-        <v>63.71875760000001</v>
+        <v>59.41128620000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1281744218976746</v>
+        <v>0.1291100695793837</v>
       </c>
       <c r="T30">
-        <v>1.651084903338089</v>
+        <v>1.669838707328753</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.103497717402775</v>
+        <v>2.671410341563714</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1073063994013624</v>
+        <v>0.1072282150363992</v>
       </c>
       <c r="C31">
-        <v>1472.908754887052</v>
+        <v>1455.725513471655</v>
       </c>
       <c r="D31">
-        <v>2043.374754887052</v>
+        <v>2045.975513471655</v>
       </c>
       <c r="E31">
-        <v>554.6359999999999</v>
+        <v>574.42</v>
       </c>
       <c r="F31">
-        <v>573.7359999999999</v>
+        <v>593.52</v>
       </c>
       <c r="G31">
         <v>3.27</v>
@@ -3939,28 +3939,28 @@
         <v>110.2</v>
       </c>
       <c r="M31">
-        <v>41.25161839999999</v>
+        <v>42.674088</v>
       </c>
       <c r="N31">
-        <v>68.9483816</v>
+        <v>67.52591200000001</v>
       </c>
       <c r="O31">
-        <v>17.2370954</v>
+        <v>16.881478</v>
       </c>
       <c r="P31">
-        <v>51.7112862</v>
+        <v>50.644434</v>
       </c>
       <c r="Q31">
-        <v>59.41128620000001</v>
+        <v>58.34443400000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1291100695793837</v>
+        <v>0.1300724500519989</v>
       </c>
       <c r="T31">
-        <v>1.669838707328753</v>
+        <v>1.68912833429058</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.671410341563715</v>
+        <v>2.582363330178257</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3985,22 +3985,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1072282150363992</v>
+        <v>0.108056780671436</v>
       </c>
       <c r="C32">
-        <v>1455.725513471655</v>
+        <v>1408.711949361427</v>
       </c>
       <c r="D32">
-        <v>2045.975513471655</v>
+        <v>2018.745949361427</v>
       </c>
       <c r="E32">
-        <v>574.42</v>
+        <v>594.204</v>
       </c>
       <c r="F32">
-        <v>593.52</v>
+        <v>613.304</v>
       </c>
       <c r="G32">
         <v>3.27</v>
@@ -4021,45 +4021,45 @@
         <v>110.2</v>
       </c>
       <c r="M32">
-        <v>42.674088</v>
+        <v>46.4884432</v>
       </c>
       <c r="N32">
-        <v>67.52591200000001</v>
+        <v>63.7115568</v>
       </c>
       <c r="O32">
-        <v>16.881478</v>
+        <v>15.9278892</v>
       </c>
       <c r="P32">
-        <v>50.644434</v>
+        <v>47.7836676</v>
       </c>
       <c r="Q32">
-        <v>58.34443400000001</v>
+        <v>55.4836676</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1300724500519989</v>
+        <v>0.1310627256107768</v>
       </c>
       <c r="T32">
-        <v>1.68912833429058</v>
+        <v>1.708977080874488</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.582363330178257</v>
+        <v>2.370481616816113</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4067,22 +4067,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.108056780671436</v>
+        <v>0.1080078463064727</v>
       </c>
       <c r="C33">
-        <v>1408.711949361427</v>
+        <v>1390.51594921867</v>
       </c>
       <c r="D33">
-        <v>2018.745949361427</v>
+        <v>2020.33394921867</v>
       </c>
       <c r="E33">
-        <v>594.204</v>
+        <v>613.9879999999999</v>
       </c>
       <c r="F33">
-        <v>613.304</v>
+        <v>633.088</v>
       </c>
       <c r="G33">
         <v>3.27</v>
@@ -4103,28 +4103,28 @@
         <v>110.2</v>
       </c>
       <c r="M33">
-        <v>46.4884432</v>
+        <v>47.9880704</v>
       </c>
       <c r="N33">
-        <v>63.7115568</v>
+        <v>62.2119296</v>
       </c>
       <c r="O33">
-        <v>15.9278892</v>
+        <v>15.5529824</v>
       </c>
       <c r="P33">
-        <v>47.7836676</v>
+        <v>46.6589472</v>
       </c>
       <c r="Q33">
-        <v>55.4836676</v>
+        <v>54.3589472</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1310627256107768</v>
+        <v>0.1320821269212834</v>
       </c>
       <c r="T33">
-        <v>1.708977080874488</v>
+        <v>1.729409614122629</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.370481616816113</v>
+        <v>2.296404066290609</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4149,22 +4149,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1080078463064727</v>
+        <v>0.1079589119415095</v>
       </c>
       <c r="C34">
-        <v>1390.51594921867</v>
+        <v>1372.322449369505</v>
       </c>
       <c r="D34">
-        <v>2020.33394921867</v>
+        <v>2021.924449369505</v>
       </c>
       <c r="E34">
-        <v>613.9879999999999</v>
+        <v>633.7719999999999</v>
       </c>
       <c r="F34">
-        <v>633.088</v>
+        <v>652.872</v>
       </c>
       <c r="G34">
         <v>3.27</v>
@@ -4185,28 +4185,28 @@
         <v>110.2</v>
       </c>
       <c r="M34">
-        <v>47.9880704</v>
+        <v>49.4876976</v>
       </c>
       <c r="N34">
-        <v>62.2119296</v>
+        <v>60.7123024</v>
       </c>
       <c r="O34">
-        <v>15.5529824</v>
+        <v>15.1780756</v>
       </c>
       <c r="P34">
-        <v>46.6589472</v>
+        <v>45.5342268</v>
       </c>
       <c r="Q34">
-        <v>54.3589472</v>
+        <v>53.2342268</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1320821269212834</v>
+        <v>0.133131958121656</v>
       </c>
       <c r="T34">
-        <v>1.729409614122629</v>
+        <v>1.750452073736385</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.296404066290609</v>
+        <v>2.226816064281802</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4231,22 +4231,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1079589119415095</v>
+        <v>0.1079099775765462</v>
       </c>
       <c r="C35">
-        <v>1372.322449369505</v>
+        <v>1354.131455723622</v>
       </c>
       <c r="D35">
-        <v>2021.924449369505</v>
+        <v>2023.517455723622</v>
       </c>
       <c r="E35">
-        <v>633.7719999999999</v>
+        <v>653.5559999999999</v>
       </c>
       <c r="F35">
-        <v>652.872</v>
+        <v>672.6559999999999</v>
       </c>
       <c r="G35">
         <v>3.27</v>
@@ -4267,28 +4267,28 @@
         <v>110.2</v>
       </c>
       <c r="M35">
-        <v>49.4876976</v>
+        <v>50.9873248</v>
       </c>
       <c r="N35">
-        <v>60.7123024</v>
+        <v>59.2126752</v>
       </c>
       <c r="O35">
-        <v>15.1780756</v>
+        <v>14.8031688</v>
       </c>
       <c r="P35">
-        <v>45.5342268</v>
+        <v>44.4095064</v>
       </c>
       <c r="Q35">
-        <v>53.2342268</v>
+        <v>52.1095064</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.133131958121656</v>
+        <v>0.1342136023887064</v>
       </c>
       <c r="T35">
-        <v>1.750452073736385</v>
+        <v>1.772132183641468</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.226816064281802</v>
+        <v>2.161321474155867</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4313,22 +4313,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1079099775765462</v>
+        <v>0.107861043211583</v>
       </c>
       <c r="C36">
-        <v>1354.131455723622</v>
+        <v>1335.942974209354</v>
       </c>
       <c r="D36">
-        <v>2023.517455723622</v>
+        <v>2025.112974209354</v>
       </c>
       <c r="E36">
-        <v>653.5559999999999</v>
+        <v>673.34</v>
       </c>
       <c r="F36">
-        <v>672.6559999999999</v>
+        <v>692.4400000000001</v>
       </c>
       <c r="G36">
         <v>3.27</v>
@@ -4349,28 +4349,28 @@
         <v>110.2</v>
       </c>
       <c r="M36">
-        <v>50.9873248</v>
+        <v>52.48695200000001</v>
       </c>
       <c r="N36">
-        <v>59.2126752</v>
+        <v>57.71304799999999</v>
       </c>
       <c r="O36">
-        <v>14.8031688</v>
+        <v>14.428262</v>
       </c>
       <c r="P36">
-        <v>44.4095064</v>
+        <v>43.284786</v>
       </c>
       <c r="Q36">
-        <v>52.1095064</v>
+        <v>50.984786</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1342136023887064</v>
+        <v>0.13532852801782</v>
       </c>
       <c r="T36">
-        <v>1.772132183641468</v>
+        <v>1.794479373851323</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.161321474155867</v>
+        <v>2.099569432037128</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.107861043211583</v>
+        <v>0.1078121088466198</v>
       </c>
       <c r="C37">
-        <v>1335.942974209354</v>
+        <v>1317.757010773743</v>
       </c>
       <c r="D37">
-        <v>2025.112974209354</v>
+        <v>2026.711010773743</v>
       </c>
       <c r="E37">
-        <v>673.34</v>
+        <v>693.124</v>
       </c>
       <c r="F37">
-        <v>692.4400000000001</v>
+        <v>712.224</v>
       </c>
       <c r="G37">
         <v>3.27</v>
@@ -4431,28 +4431,28 @@
         <v>110.2</v>
       </c>
       <c r="M37">
-        <v>52.48695200000001</v>
+        <v>53.98657920000001</v>
       </c>
       <c r="N37">
-        <v>57.71304799999999</v>
+        <v>56.21342079999999</v>
       </c>
       <c r="O37">
-        <v>14.428262</v>
+        <v>14.0533552</v>
       </c>
       <c r="P37">
-        <v>43.284786</v>
+        <v>42.1600656</v>
       </c>
       <c r="Q37">
-        <v>50.984786</v>
+        <v>49.8600656</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.13532852801782</v>
+        <v>0.1364782950728434</v>
       </c>
       <c r="T37">
-        <v>1.794479373851323</v>
+        <v>1.817524913755235</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.099569432037128</v>
+        <v>2.041248058924985</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1078121088466198</v>
+        <v>0.1117036744816565</v>
       </c>
       <c r="C38">
-        <v>1317.757010773742</v>
+        <v>1178.297150759701</v>
       </c>
       <c r="D38">
-        <v>2026.711010773742</v>
+        <v>1907.035150759701</v>
       </c>
       <c r="E38">
-        <v>693.1239999999999</v>
+        <v>712.9079999999999</v>
       </c>
       <c r="F38">
-        <v>712.2239999999999</v>
+        <v>732.0079999999999</v>
       </c>
       <c r="G38">
         <v>3.27</v>
@@ -4513,45 +4513,45 @@
         <v>110.2</v>
       </c>
       <c r="M38">
-        <v>53.9865792</v>
+        <v>65.88072</v>
       </c>
       <c r="N38">
-        <v>56.2134208</v>
+        <v>44.31928000000001</v>
       </c>
       <c r="O38">
-        <v>14.0533552</v>
+        <v>11.07982</v>
       </c>
       <c r="P38">
-        <v>42.1600656</v>
+        <v>33.23946000000001</v>
       </c>
       <c r="Q38">
-        <v>49.86006560000001</v>
+        <v>40.93946000000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1364782950728434</v>
+        <v>0.1376645626692961</v>
       </c>
       <c r="T38">
-        <v>1.817524913755235</v>
+        <v>1.841302058100542</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.041248058924985</v>
+        <v>1.67272003098934</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1117036744816565</v>
+        <v>0.1117612401166933</v>
       </c>
       <c r="C39">
-        <v>1178.297150759701</v>
+        <v>1156.848844732454</v>
       </c>
       <c r="D39">
-        <v>1907.035150759701</v>
+        <v>1905.370844732454</v>
       </c>
       <c r="E39">
-        <v>712.9079999999999</v>
+        <v>732.6919999999999</v>
       </c>
       <c r="F39">
-        <v>732.0079999999999</v>
+        <v>751.7919999999999</v>
       </c>
       <c r="G39">
         <v>3.27</v>
@@ -4595,28 +4595,28 @@
         <v>110.2</v>
       </c>
       <c r="M39">
-        <v>65.88072</v>
+        <v>67.66127999999999</v>
       </c>
       <c r="N39">
-        <v>44.31928000000001</v>
+        <v>42.53872000000001</v>
       </c>
       <c r="O39">
-        <v>11.07982</v>
+        <v>10.63468</v>
       </c>
       <c r="P39">
-        <v>33.23946000000001</v>
+        <v>31.90404000000001</v>
       </c>
       <c r="Q39">
-        <v>40.93946000000001</v>
+        <v>39.60404000000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1376645626692961</v>
+        <v>0.1388890969624085</v>
       </c>
       <c r="T39">
-        <v>1.841302058100542</v>
+        <v>1.865846207102148</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.67272003098934</v>
+        <v>1.62870108280541</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4641,22 +4641,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1117612401166933</v>
+        <v>0.11181880575173</v>
       </c>
       <c r="C40">
-        <v>1156.848844732454</v>
+        <v>1135.403441115581</v>
       </c>
       <c r="D40">
-        <v>1905.370844732454</v>
+        <v>1903.709441115581</v>
       </c>
       <c r="E40">
-        <v>732.6919999999999</v>
+        <v>752.476</v>
       </c>
       <c r="F40">
-        <v>751.7919999999999</v>
+        <v>771.576</v>
       </c>
       <c r="G40">
         <v>3.27</v>
@@ -4677,28 +4677,28 @@
         <v>110.2</v>
       </c>
       <c r="M40">
-        <v>67.66127999999999</v>
+        <v>69.44184</v>
       </c>
       <c r="N40">
-        <v>42.53872000000001</v>
+        <v>40.75816</v>
       </c>
       <c r="O40">
-        <v>10.63468</v>
+        <v>10.18954</v>
       </c>
       <c r="P40">
-        <v>31.90404000000001</v>
+        <v>30.56862</v>
       </c>
       <c r="Q40">
-        <v>39.60404000000001</v>
+        <v>38.26862000000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1388890969624085</v>
+        <v>0.1401537799208689</v>
       </c>
       <c r="T40">
-        <v>1.865846207102148</v>
+        <v>1.891195082300529</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.62870108280541</v>
+        <v>1.58693951657963</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.11181880575173</v>
+        <v>0.1118763713867668</v>
       </c>
       <c r="C41">
-        <v>1135.403441115581</v>
+        <v>1113.960932323355</v>
       </c>
       <c r="D41">
-        <v>1903.709441115581</v>
+        <v>1902.050932323355</v>
       </c>
       <c r="E41">
-        <v>752.476</v>
+        <v>772.26</v>
       </c>
       <c r="F41">
-        <v>771.576</v>
+        <v>791.36</v>
       </c>
       <c r="G41">
         <v>3.27</v>
@@ -4759,28 +4759,28 @@
         <v>110.2</v>
       </c>
       <c r="M41">
-        <v>69.44184</v>
+        <v>71.22239999999999</v>
       </c>
       <c r="N41">
-        <v>40.75816</v>
+        <v>38.97760000000001</v>
       </c>
       <c r="O41">
-        <v>10.18954</v>
+        <v>9.744400000000002</v>
       </c>
       <c r="P41">
-        <v>30.56862</v>
+        <v>29.23320000000001</v>
       </c>
       <c r="Q41">
-        <v>38.26862000000001</v>
+        <v>36.93320000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1401537799208689</v>
+        <v>0.1414606189779447</v>
       </c>
       <c r="T41">
-        <v>1.891195082300529</v>
+        <v>1.917388920005523</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.58693951657963</v>
+        <v>1.547266028665139</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1118763713867668</v>
+        <v>0.1119339370218036</v>
       </c>
       <c r="C42">
-        <v>1113.960932323355</v>
+        <v>1092.521310796463</v>
       </c>
       <c r="D42">
-        <v>1902.050932323355</v>
+        <v>1900.395310796463</v>
       </c>
       <c r="E42">
-        <v>772.26</v>
+        <v>792.044</v>
       </c>
       <c r="F42">
-        <v>791.36</v>
+        <v>811.144</v>
       </c>
       <c r="G42">
         <v>3.27</v>
@@ -4841,28 +4841,28 @@
         <v>110.2</v>
       </c>
       <c r="M42">
-        <v>71.22239999999999</v>
+        <v>73.00296</v>
       </c>
       <c r="N42">
-        <v>38.97760000000001</v>
+        <v>37.19704</v>
       </c>
       <c r="O42">
-        <v>9.744400000000002</v>
+        <v>9.29926</v>
       </c>
       <c r="P42">
-        <v>29.23320000000001</v>
+        <v>27.89778</v>
       </c>
       <c r="Q42">
-        <v>36.93320000000001</v>
+        <v>35.59778</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1414606189779447</v>
+        <v>0.1428117576640738</v>
       </c>
       <c r="T42">
-        <v>1.917388920005523</v>
+        <v>1.944470684412381</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.547266028665139</v>
+        <v>1.509527832844038</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1119339370218036</v>
+        <v>0.1320187975300764</v>
       </c>
       <c r="C43">
-        <v>1092.521310796463</v>
+        <v>630.0359994657416</v>
       </c>
       <c r="D43">
-        <v>1900.395310796463</v>
+        <v>1457.693999465742</v>
       </c>
       <c r="E43">
-        <v>792.044</v>
+        <v>811.828</v>
       </c>
       <c r="F43">
-        <v>811.144</v>
+        <v>830.928</v>
       </c>
       <c r="G43">
         <v>3.27</v>
@@ -4923,45 +4923,45 @@
         <v>110.2</v>
       </c>
       <c r="M43">
-        <v>73.00296</v>
+        <v>121.9802304</v>
       </c>
       <c r="N43">
-        <v>37.19704</v>
+        <v>-11.78023040000001</v>
       </c>
       <c r="O43">
-        <v>9.29926</v>
+        <v>-2.945057600000002</v>
       </c>
       <c r="P43">
-        <v>27.89778</v>
+        <v>-8.835172800000006</v>
       </c>
       <c r="Q43">
-        <v>35.59778</v>
+        <v>-1.135172800000003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1428117576640738</v>
+        <v>0.145324468600108</v>
       </c>
       <c r="T43">
-        <v>1.944470684412381</v>
+        <v>1.994834608035324</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.25</v>
+        <v>0.2258562712142573</v>
       </c>
       <c r="W43">
-        <v>0.0675</v>
+        <v>0.113644299385747</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.509527832844038</v>
+        <v>0.9034250848570293</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1320187975300764</v>
+        <v>0.1330287975300764</v>
       </c>
       <c r="C44">
-        <v>630.0359994657417</v>
+        <v>593.3737324123327</v>
       </c>
       <c r="D44">
-        <v>1457.693999465742</v>
+        <v>1440.815732412333</v>
       </c>
       <c r="E44">
-        <v>811.8279999999999</v>
+        <v>831.6119999999999</v>
       </c>
       <c r="F44">
-        <v>830.9279999999999</v>
+        <v>850.7119999999999</v>
       </c>
       <c r="G44">
         <v>3.27</v>
@@ -5005,37 +5005,37 @@
         <v>110.2</v>
       </c>
       <c r="M44">
-        <v>121.9802304</v>
+        <v>124.8845216</v>
       </c>
       <c r="N44">
-        <v>-11.78023039999999</v>
+        <v>-14.6845216</v>
       </c>
       <c r="O44">
-        <v>-2.945057599999998</v>
+        <v>-3.671130399999999</v>
       </c>
       <c r="P44">
-        <v>-8.835172799999995</v>
+        <v>-11.0133912</v>
       </c>
       <c r="Q44">
-        <v>-1.135172799999992</v>
+        <v>-3.313391199999995</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.145324468600108</v>
+        <v>0.1470705119088818</v>
       </c>
       <c r="T44">
-        <v>1.994834608035323</v>
+        <v>2.029831706421908</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2258562712142574</v>
+        <v>0.22060379979067</v>
       </c>
       <c r="W44">
-        <v>0.113644299385747</v>
+        <v>0.1144153621907296</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9034250848570294</v>
+        <v>0.88241519916268</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5051,22 +5051,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1330287975300764</v>
+        <v>0.1340387975300764</v>
       </c>
       <c r="C45">
-        <v>593.3737324123327</v>
+        <v>557.0978498111393</v>
       </c>
       <c r="D45">
-        <v>1440.815732412333</v>
+        <v>1424.323849811139</v>
       </c>
       <c r="E45">
-        <v>831.6119999999999</v>
+        <v>851.396</v>
       </c>
       <c r="F45">
-        <v>850.7119999999999</v>
+        <v>870.496</v>
       </c>
       <c r="G45">
         <v>3.27</v>
@@ -5087,37 +5087,37 @@
         <v>110.2</v>
       </c>
       <c r="M45">
-        <v>124.8845216</v>
+        <v>127.7888128</v>
       </c>
       <c r="N45">
-        <v>-14.6845216</v>
+        <v>-17.5888128</v>
       </c>
       <c r="O45">
-        <v>-3.671130399999999</v>
+        <v>-4.3972032</v>
       </c>
       <c r="P45">
-        <v>-11.0133912</v>
+        <v>-13.1916096</v>
       </c>
       <c r="Q45">
-        <v>-3.313391199999995</v>
+        <v>-5.491609599999997</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1470705119088818</v>
+        <v>0.1488789139072547</v>
       </c>
       <c r="T45">
-        <v>2.029831706421908</v>
+        <v>2.066078701179442</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.22060379979067</v>
+        <v>0.2155900770681548</v>
       </c>
       <c r="W45">
-        <v>0.1144153621907296</v>
+        <v>0.1151513766863949</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.88241519916268</v>
+        <v>0.862360308272619</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1340387975300764</v>
+        <v>0.1350487975300764</v>
       </c>
       <c r="C46">
-        <v>557.0978498111393</v>
+        <v>521.1952338956203</v>
       </c>
       <c r="D46">
-        <v>1424.323849811139</v>
+        <v>1408.20523389562</v>
       </c>
       <c r="E46">
-        <v>851.396</v>
+        <v>871.1799999999999</v>
       </c>
       <c r="F46">
-        <v>870.496</v>
+        <v>890.28</v>
       </c>
       <c r="G46">
         <v>3.27</v>
@@ -5169,37 +5169,37 @@
         <v>110.2</v>
       </c>
       <c r="M46">
-        <v>127.7888128</v>
+        <v>130.693104</v>
       </c>
       <c r="N46">
-        <v>-17.5888128</v>
+        <v>-20.493104</v>
       </c>
       <c r="O46">
-        <v>-4.3972032</v>
+        <v>-5.123276000000001</v>
       </c>
       <c r="P46">
-        <v>-13.1916096</v>
+        <v>-15.369828</v>
       </c>
       <c r="Q46">
-        <v>-5.491609599999997</v>
+        <v>-7.669827999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1488789139072547</v>
+        <v>0.1507530759782957</v>
       </c>
       <c r="T46">
-        <v>2.066078701179442</v>
+        <v>2.103643768473614</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2155900770681548</v>
+        <v>0.2107991864666402</v>
       </c>
       <c r="W46">
-        <v>0.1151513766863949</v>
+        <v>0.1158546794266972</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.862360308272619</v>
+        <v>0.8431967458665608</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5215,22 +5215,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1350487975300764</v>
+        <v>0.1360587975300764</v>
       </c>
       <c r="C47">
-        <v>521.1952338956203</v>
+        <v>485.6533540528202</v>
       </c>
       <c r="D47">
-        <v>1408.20523389562</v>
+        <v>1392.44735405282</v>
       </c>
       <c r="E47">
-        <v>871.1799999999999</v>
+        <v>890.9639999999999</v>
       </c>
       <c r="F47">
-        <v>890.28</v>
+        <v>910.064</v>
       </c>
       <c r="G47">
         <v>3.27</v>
@@ -5251,37 +5251,37 @@
         <v>110.2</v>
       </c>
       <c r="M47">
-        <v>130.693104</v>
+        <v>133.5973952</v>
       </c>
       <c r="N47">
-        <v>-20.493104</v>
+        <v>-23.39739519999999</v>
       </c>
       <c r="O47">
-        <v>-5.123276000000001</v>
+        <v>-5.849348799999998</v>
       </c>
       <c r="P47">
-        <v>-15.369828</v>
+        <v>-17.54804639999999</v>
       </c>
       <c r="Q47">
-        <v>-7.669827999999999</v>
+        <v>-9.848046399999991</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1507530759782957</v>
+        <v>0.1526966514593753</v>
       </c>
       <c r="T47">
-        <v>2.103643768473614</v>
+        <v>2.142600134556458</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2107991864666402</v>
+        <v>0.2062165954564959</v>
       </c>
       <c r="W47">
-        <v>0.1158546794266972</v>
+        <v>0.1165274037869864</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8431967458665608</v>
+        <v>0.8248663818259834</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5297,22 +5297,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1360587975300764</v>
+        <v>0.1370687975300764</v>
       </c>
       <c r="C48">
-        <v>485.6533540528202</v>
+        <v>450.460234335538</v>
       </c>
       <c r="D48">
-        <v>1392.44735405282</v>
+        <v>1377.038234335538</v>
       </c>
       <c r="E48">
-        <v>890.9639999999999</v>
+        <v>910.7479999999999</v>
       </c>
       <c r="F48">
-        <v>910.064</v>
+        <v>929.848</v>
       </c>
       <c r="G48">
         <v>3.27</v>
@@ -5333,37 +5333,37 @@
         <v>110.2</v>
       </c>
       <c r="M48">
-        <v>133.5973952</v>
+        <v>136.5016864</v>
       </c>
       <c r="N48">
-        <v>-23.39739519999999</v>
+        <v>-26.30168640000001</v>
       </c>
       <c r="O48">
-        <v>-5.849348799999998</v>
+        <v>-6.575421600000002</v>
       </c>
       <c r="P48">
-        <v>-17.54804639999999</v>
+        <v>-19.72626480000001</v>
       </c>
       <c r="Q48">
-        <v>-9.848046399999991</v>
+        <v>-12.0262648</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1526966514593753</v>
+        <v>0.154713569411439</v>
       </c>
       <c r="T48">
-        <v>2.142600134556458</v>
+        <v>2.183026552189599</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2062165954564959</v>
+        <v>0.2018290083191236</v>
       </c>
       <c r="W48">
-        <v>0.1165274037869864</v>
+        <v>0.1171715015787527</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8248663818259834</v>
+        <v>0.8073160332764944</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1370687975300764</v>
+        <v>0.1656256696747508</v>
       </c>
       <c r="C49">
-        <v>450.460234335538</v>
+        <v>102.5002691772611</v>
       </c>
       <c r="D49">
-        <v>1377.038234335538</v>
+        <v>1048.862269177261</v>
       </c>
       <c r="E49">
-        <v>910.7479999999999</v>
+        <v>930.532</v>
       </c>
       <c r="F49">
-        <v>929.848</v>
+        <v>949.6320000000001</v>
       </c>
       <c r="G49">
         <v>3.27</v>
@@ -5415,45 +5415,45 @@
         <v>110.2</v>
       </c>
       <c r="M49">
-        <v>136.5016864</v>
+        <v>190.6861056</v>
       </c>
       <c r="N49">
-        <v>-26.30168640000001</v>
+        <v>-80.48610560000002</v>
       </c>
       <c r="O49">
-        <v>-6.575421600000002</v>
+        <v>-20.1215264</v>
       </c>
       <c r="P49">
-        <v>-19.72626480000001</v>
+        <v>-60.36457920000001</v>
       </c>
       <c r="Q49">
-        <v>-12.0262648</v>
+        <v>-52.66457920000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.154713569411439</v>
+        <v>0.1599366614091098</v>
       </c>
       <c r="T49">
-        <v>2.183026552189599</v>
+        <v>2.287716432220717</v>
       </c>
       <c r="U49">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.2018290083191236</v>
+        <v>0.1444782770790406</v>
       </c>
       <c r="W49">
-        <v>0.1171715015787527</v>
+        <v>0.1717887619625287</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8073160332764944</v>
+        <v>0.5779131083161624</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1656256696747508</v>
+        <v>0.1671756696747508</v>
       </c>
       <c r="C50">
-        <v>102.5002691772612</v>
+        <v>69.32201543941392</v>
       </c>
       <c r="D50">
-        <v>1048.862269177261</v>
+        <v>1035.468015439414</v>
       </c>
       <c r="E50">
-        <v>930.5319999999999</v>
+        <v>950.3159999999999</v>
       </c>
       <c r="F50">
-        <v>949.6319999999999</v>
+        <v>969.4159999999999</v>
       </c>
       <c r="G50">
         <v>3.27</v>
@@ -5497,37 +5497,37 @@
         <v>110.2</v>
       </c>
       <c r="M50">
-        <v>190.6861056</v>
+        <v>194.6587328</v>
       </c>
       <c r="N50">
-        <v>-80.48610559999999</v>
+        <v>-84.45873279999999</v>
       </c>
       <c r="O50">
-        <v>-20.1215264</v>
+        <v>-21.1146832</v>
       </c>
       <c r="P50">
-        <v>-60.36457919999999</v>
+        <v>-63.34404959999999</v>
       </c>
       <c r="Q50">
-        <v>-52.66457919999999</v>
+        <v>-55.64404959999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1599366614091098</v>
+        <v>0.1621746351622296</v>
       </c>
       <c r="T50">
-        <v>2.287716432220717</v>
+        <v>2.332573617166221</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1444782770790406</v>
+        <v>0.1415297408121214</v>
       </c>
       <c r="W50">
-        <v>0.1717887619625287</v>
+        <v>0.172380828044926</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5779131083161626</v>
+        <v>0.5661189632484858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5543,22 +5543,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1671756696747508</v>
+        <v>0.1687256696747508</v>
       </c>
       <c r="C51">
-        <v>69.32201543941392</v>
+        <v>36.48154458041688</v>
       </c>
       <c r="D51">
-        <v>1035.468015439414</v>
+        <v>1022.411544580417</v>
       </c>
       <c r="E51">
-        <v>950.3159999999999</v>
+        <v>970.0999999999999</v>
       </c>
       <c r="F51">
-        <v>969.4159999999999</v>
+        <v>989.1999999999999</v>
       </c>
       <c r="G51">
         <v>3.27</v>
@@ -5579,37 +5579,37 @@
         <v>110.2</v>
       </c>
       <c r="M51">
-        <v>194.6587328</v>
+        <v>198.63136</v>
       </c>
       <c r="N51">
-        <v>-84.45873279999999</v>
+        <v>-88.43136</v>
       </c>
       <c r="O51">
-        <v>-21.1146832</v>
+        <v>-22.10784</v>
       </c>
       <c r="P51">
-        <v>-63.34404959999999</v>
+        <v>-66.32352</v>
       </c>
       <c r="Q51">
-        <v>-55.64404959999999</v>
+        <v>-58.62352</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1621746351622296</v>
+        <v>0.1645021278654742</v>
       </c>
       <c r="T51">
-        <v>2.332573617166221</v>
+        <v>2.379225089509546</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1415297408121214</v>
+        <v>0.138699145995879</v>
       </c>
       <c r="W51">
-        <v>0.172380828044926</v>
+        <v>0.1729492114840275</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5661189632484858</v>
+        <v>0.5547965839835161</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1687256696747508</v>
+        <v>0.1702756696747508</v>
       </c>
       <c r="C52">
-        <v>36.48154458041688</v>
+        <v>3.966238147276158</v>
       </c>
       <c r="D52">
-        <v>1022.411544580417</v>
+        <v>1009.680238147276</v>
       </c>
       <c r="E52">
-        <v>970.0999999999999</v>
+        <v>989.8839999999999</v>
       </c>
       <c r="F52">
-        <v>989.1999999999999</v>
+        <v>1008.984</v>
       </c>
       <c r="G52">
         <v>3.27</v>
@@ -5661,37 +5661,37 @@
         <v>110.2</v>
       </c>
       <c r="M52">
-        <v>198.63136</v>
+        <v>202.6039872</v>
       </c>
       <c r="N52">
-        <v>-88.43136</v>
+        <v>-92.40398719999997</v>
       </c>
       <c r="O52">
-        <v>-22.10784</v>
+        <v>-23.10099679999999</v>
       </c>
       <c r="P52">
-        <v>-66.32352</v>
+        <v>-69.30299039999998</v>
       </c>
       <c r="Q52">
-        <v>-58.62352</v>
+        <v>-61.60299039999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1645021278654742</v>
+        <v>0.166924620270892</v>
       </c>
       <c r="T52">
-        <v>2.379225089509546</v>
+        <v>2.427780703581169</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.138699145995879</v>
+        <v>0.1359795548979206</v>
       </c>
       <c r="W52">
-        <v>0.1729492114840275</v>
+        <v>0.1734953053764975</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5547965839835161</v>
+        <v>0.5439182195916824</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5707,22 +5707,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1702756696747508</v>
+        <v>0.1718256696747508</v>
       </c>
       <c r="C53">
-        <v>3.966238147276158</v>
+        <v>-28.23590153146768</v>
       </c>
       <c r="D53">
-        <v>1009.680238147276</v>
+        <v>997.2620984685324</v>
       </c>
       <c r="E53">
-        <v>989.8839999999999</v>
+        <v>1009.668</v>
       </c>
       <c r="F53">
-        <v>1008.984</v>
+        <v>1028.768</v>
       </c>
       <c r="G53">
         <v>3.27</v>
@@ -5743,37 +5743,37 @@
         <v>110.2</v>
       </c>
       <c r="M53">
-        <v>202.6039872</v>
+        <v>206.5766144</v>
       </c>
       <c r="N53">
-        <v>-92.40398719999997</v>
+        <v>-96.37661440000001</v>
       </c>
       <c r="O53">
-        <v>-23.10099679999999</v>
+        <v>-24.0941536</v>
       </c>
       <c r="P53">
-        <v>-69.30299039999998</v>
+        <v>-72.28246080000001</v>
       </c>
       <c r="Q53">
-        <v>-61.60299039999998</v>
+        <v>-64.58246080000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.166924620270892</v>
+        <v>0.1694480498598689</v>
       </c>
       <c r="T53">
-        <v>2.427780703581169</v>
+        <v>2.47835946823911</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1359795548979206</v>
+        <v>0.133364563457576</v>
       </c>
       <c r="W53">
-        <v>0.1734953053764975</v>
+        <v>0.1740203956577188</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5439182195916824</v>
+        <v>0.5334582538303039</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1718256696747508</v>
+        <v>0.1733756696747508</v>
       </c>
       <c r="C54">
-        <v>-28.23590153146768</v>
+        <v>-60.13628905713824</v>
       </c>
       <c r="D54">
-        <v>997.2620984685324</v>
+        <v>985.1457109428617</v>
       </c>
       <c r="E54">
-        <v>1009.668</v>
+        <v>1029.452</v>
       </c>
       <c r="F54">
-        <v>1028.768</v>
+        <v>1048.552</v>
       </c>
       <c r="G54">
         <v>3.27</v>
@@ -5825,37 +5825,37 @@
         <v>110.2</v>
       </c>
       <c r="M54">
-        <v>206.5766144</v>
+        <v>210.5492416</v>
       </c>
       <c r="N54">
-        <v>-96.37661440000001</v>
+        <v>-100.3492416</v>
       </c>
       <c r="O54">
-        <v>-24.0941536</v>
+        <v>-25.0873104</v>
       </c>
       <c r="P54">
-        <v>-72.28246080000001</v>
+        <v>-75.26193119999999</v>
       </c>
       <c r="Q54">
-        <v>-64.58246080000001</v>
+        <v>-67.56193119999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1694480498598689</v>
+        <v>0.1720788594313555</v>
       </c>
       <c r="T54">
-        <v>2.47835946823911</v>
+        <v>2.531090520754836</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.133364563457576</v>
+        <v>0.1308482509395085</v>
       </c>
       <c r="W54">
-        <v>0.1740203956577188</v>
+        <v>0.1745256712113467</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5334582538303039</v>
+        <v>0.523393003758034</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5871,22 +5871,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1733756696747508</v>
+        <v>0.1749256696747508</v>
       </c>
       <c r="C55">
-        <v>-60.13628905713824</v>
+        <v>-91.74579095623903</v>
       </c>
       <c r="D55">
-        <v>985.1457109428617</v>
+        <v>973.320209043761</v>
       </c>
       <c r="E55">
-        <v>1029.452</v>
+        <v>1049.236</v>
       </c>
       <c r="F55">
-        <v>1048.552</v>
+        <v>1068.336</v>
       </c>
       <c r="G55">
         <v>3.27</v>
@@ -5907,37 +5907,37 @@
         <v>110.2</v>
       </c>
       <c r="M55">
-        <v>210.5492416</v>
+        <v>214.5218688</v>
       </c>
       <c r="N55">
-        <v>-100.3492416</v>
+        <v>-104.3218688</v>
       </c>
       <c r="O55">
-        <v>-25.0873104</v>
+        <v>-26.0804672</v>
       </c>
       <c r="P55">
-        <v>-75.26193119999999</v>
+        <v>-78.24140160000002</v>
       </c>
       <c r="Q55">
-        <v>-67.56193119999999</v>
+        <v>-70.54140160000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1720788594313555</v>
+        <v>0.1748240520276893</v>
       </c>
       <c r="T55">
-        <v>2.531090520754836</v>
+        <v>2.586114227727768</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1308482509395085</v>
+        <v>0.1284251351813694</v>
       </c>
       <c r="W55">
-        <v>0.1745256712113467</v>
+        <v>0.175012232855581</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.523393003758034</v>
+        <v>0.5137005407254778</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1749256696747508</v>
+        <v>0.1764756696747509</v>
       </c>
       <c r="C56">
-        <v>-91.74579095623903</v>
+        <v>-123.0747581852028</v>
       </c>
       <c r="D56">
-        <v>973.320209043761</v>
+        <v>961.7752418147974</v>
       </c>
       <c r="E56">
-        <v>1049.236</v>
+        <v>1069.02</v>
       </c>
       <c r="F56">
-        <v>1068.336</v>
+        <v>1088.12</v>
       </c>
       <c r="G56">
         <v>3.27</v>
@@ -5989,37 +5989,37 @@
         <v>110.2</v>
       </c>
       <c r="M56">
-        <v>214.5218688</v>
+        <v>218.494496</v>
       </c>
       <c r="N56">
-        <v>-104.3218688</v>
+        <v>-108.294496</v>
       </c>
       <c r="O56">
-        <v>-26.0804672</v>
+        <v>-27.07362400000001</v>
       </c>
       <c r="P56">
-        <v>-78.24140160000002</v>
+        <v>-81.22087200000001</v>
       </c>
       <c r="Q56">
-        <v>-70.54140160000001</v>
+        <v>-73.52087200000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1748240520276893</v>
+        <v>0.1776912531838602</v>
       </c>
       <c r="T56">
-        <v>2.586114227727768</v>
+        <v>2.643583432788385</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1284251351813694</v>
+        <v>0.1260901327235263</v>
       </c>
       <c r="W56">
-        <v>0.175012232855581</v>
+        <v>0.1754811013491159</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5137005407254778</v>
+        <v>0.5043605308941055</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6035,22 +6035,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1764756696747509</v>
+        <v>0.1982821322355633</v>
       </c>
       <c r="C57">
-        <v>-123.0747581852028</v>
+        <v>-280.4021902914018</v>
       </c>
       <c r="D57">
-        <v>961.7752418147974</v>
+        <v>824.2318097085982</v>
       </c>
       <c r="E57">
-        <v>1069.02</v>
+        <v>1088.804</v>
       </c>
       <c r="F57">
-        <v>1088.12</v>
+        <v>1107.904</v>
       </c>
       <c r="G57">
         <v>3.27</v>
@@ -6071,45 +6071,45 @@
         <v>110.2</v>
       </c>
       <c r="M57">
-        <v>218.494496</v>
+        <v>261.2437632</v>
       </c>
       <c r="N57">
-        <v>-108.294496</v>
+        <v>-151.0437632</v>
       </c>
       <c r="O57">
-        <v>-27.07362400000001</v>
+        <v>-37.7609408</v>
       </c>
       <c r="P57">
-        <v>-81.22087200000001</v>
+        <v>-113.2828224</v>
       </c>
       <c r="Q57">
-        <v>-73.52087200000001</v>
+        <v>-105.5828224</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1776912531838602</v>
+        <v>0.1821807420307944</v>
       </c>
       <c r="T57">
-        <v>2.643583432788385</v>
+        <v>2.733569220707912</v>
       </c>
       <c r="U57">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1260901327235263</v>
+        <v>0.1054570630224331</v>
       </c>
       <c r="W57">
-        <v>0.1754811013491159</v>
+        <v>0.2109332245393103</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5043605308941055</v>
+        <v>0.4218282520897325</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6117,22 +6117,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1982821322355633</v>
+        <v>0.2001821322355633</v>
       </c>
       <c r="C58">
-        <v>-280.4021902914018</v>
+        <v>-310.3301131390073</v>
       </c>
       <c r="D58">
-        <v>824.2318097085982</v>
+        <v>814.0878868609929</v>
       </c>
       <c r="E58">
-        <v>1088.804</v>
+        <v>1108.588</v>
       </c>
       <c r="F58">
-        <v>1107.904</v>
+        <v>1127.688</v>
       </c>
       <c r="G58">
         <v>3.27</v>
@@ -6153,37 +6153,37 @@
         <v>110.2</v>
       </c>
       <c r="M58">
-        <v>261.2437632</v>
+        <v>265.9088304000001</v>
       </c>
       <c r="N58">
-        <v>-151.0437632</v>
+        <v>-155.7088304000001</v>
       </c>
       <c r="O58">
-        <v>-37.7609408</v>
+        <v>-38.92720760000002</v>
       </c>
       <c r="P58">
-        <v>-113.2828224</v>
+        <v>-116.7816228000001</v>
       </c>
       <c r="Q58">
-        <v>-105.5828224</v>
+        <v>-109.0816228</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1821807420307944</v>
+        <v>0.1853523871943013</v>
       </c>
       <c r="T58">
-        <v>2.733569220707912</v>
+        <v>2.797140597933678</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1054570630224331</v>
+        <v>0.1036069391097589</v>
       </c>
       <c r="W58">
-        <v>0.2109332245393103</v>
+        <v>0.2113694837579189</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4218282520897325</v>
+        <v>0.4144277564390354</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6199,22 +6199,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2001821322355633</v>
+        <v>0.2020821322355633</v>
       </c>
       <c r="C59">
-        <v>-310.3301131390073</v>
+        <v>-340.0113865055138</v>
       </c>
       <c r="D59">
-        <v>814.0878868609929</v>
+        <v>804.1906134944862</v>
       </c>
       <c r="E59">
-        <v>1108.588</v>
+        <v>1128.372</v>
       </c>
       <c r="F59">
-        <v>1127.688</v>
+        <v>1147.472</v>
       </c>
       <c r="G59">
         <v>3.27</v>
@@ -6235,37 +6235,37 @@
         <v>110.2</v>
       </c>
       <c r="M59">
-        <v>265.9088304000001</v>
+        <v>270.5738976</v>
       </c>
       <c r="N59">
-        <v>-155.7088304000001</v>
+        <v>-160.3738976</v>
       </c>
       <c r="O59">
-        <v>-38.92720760000002</v>
+        <v>-40.09347440000001</v>
       </c>
       <c r="P59">
-        <v>-116.7816228000001</v>
+        <v>-120.2804232</v>
       </c>
       <c r="Q59">
-        <v>-109.0816228</v>
+        <v>-112.5804232</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1853523871943013</v>
+        <v>0.1886750630798799</v>
       </c>
       <c r="T59">
-        <v>2.797140597933678</v>
+        <v>2.863739183598766</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1036069391097589</v>
+        <v>0.1018206125733837</v>
       </c>
       <c r="W59">
-        <v>0.2113694837579189</v>
+        <v>0.2117906995551961</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4144277564390354</v>
+        <v>0.4072824502935348</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2020821322355633</v>
+        <v>0.2039821322355633</v>
       </c>
       <c r="C60">
-        <v>-340.0113865055133</v>
+        <v>-369.4548982597494</v>
       </c>
       <c r="D60">
-        <v>804.1906134944865</v>
+        <v>794.5311017402505</v>
       </c>
       <c r="E60">
-        <v>1128.372</v>
+        <v>1148.156</v>
       </c>
       <c r="F60">
-        <v>1147.472</v>
+        <v>1167.256</v>
       </c>
       <c r="G60">
         <v>3.27</v>
@@ -6317,37 +6317,37 @@
         <v>110.2</v>
       </c>
       <c r="M60">
-        <v>270.5738976</v>
+        <v>275.2389648</v>
       </c>
       <c r="N60">
-        <v>-160.3738976</v>
+        <v>-165.0389648</v>
       </c>
       <c r="O60">
-        <v>-40.09347439999999</v>
+        <v>-41.25974119999999</v>
       </c>
       <c r="P60">
-        <v>-120.2804232</v>
+        <v>-123.7792236</v>
       </c>
       <c r="Q60">
-        <v>-112.5804232</v>
+        <v>-116.0792236</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1886750630798799</v>
+        <v>0.1921598207159745</v>
       </c>
       <c r="T60">
-        <v>2.863739183598764</v>
+        <v>2.93358648075971</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1018206125733837</v>
+        <v>0.1000948394789196</v>
       </c>
       <c r="W60">
-        <v>0.2117906995551961</v>
+        <v>0.2121976368508708</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4072824502935349</v>
+        <v>0.4003793579156784</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6363,22 +6363,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2039821322355633</v>
+        <v>0.2058821322355633</v>
       </c>
       <c r="C61">
-        <v>-369.4548982597494</v>
+        <v>-398.6691143133754</v>
       </c>
       <c r="D61">
-        <v>794.5311017402505</v>
+        <v>785.1008856866246</v>
       </c>
       <c r="E61">
-        <v>1148.156</v>
+        <v>1167.94</v>
       </c>
       <c r="F61">
-        <v>1167.256</v>
+        <v>1187.04</v>
       </c>
       <c r="G61">
         <v>3.27</v>
@@ -6399,37 +6399,37 @@
         <v>110.2</v>
       </c>
       <c r="M61">
-        <v>275.2389648</v>
+        <v>279.904032</v>
       </c>
       <c r="N61">
-        <v>-165.0389648</v>
+        <v>-169.704032</v>
       </c>
       <c r="O61">
-        <v>-41.25974119999999</v>
+        <v>-42.42600800000001</v>
       </c>
       <c r="P61">
-        <v>-123.7792236</v>
+        <v>-127.278024</v>
       </c>
       <c r="Q61">
-        <v>-116.0792236</v>
+        <v>-119.578024</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1921598207159745</v>
+        <v>0.1958188162338738</v>
       </c>
       <c r="T61">
-        <v>2.93358648075971</v>
+        <v>3.006926142778703</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1000948394789196</v>
+        <v>0.09842659215427092</v>
       </c>
       <c r="W61">
-        <v>0.2121976368508708</v>
+        <v>0.2125910095700229</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4003793579156784</v>
+        <v>0.3937063686170836</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6445,22 +6445,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2058821322355633</v>
+        <v>0.2077821322355633</v>
       </c>
       <c r="C62">
-        <v>-398.6691143133754</v>
+        <v>-427.6621033680156</v>
       </c>
       <c r="D62">
-        <v>785.1008856866246</v>
+        <v>775.8918966319843</v>
       </c>
       <c r="E62">
-        <v>1167.94</v>
+        <v>1187.724</v>
       </c>
       <c r="F62">
-        <v>1187.04</v>
+        <v>1206.824</v>
       </c>
       <c r="G62">
         <v>3.27</v>
@@ -6481,37 +6481,37 @@
         <v>110.2</v>
       </c>
       <c r="M62">
-        <v>279.904032</v>
+        <v>284.5690992</v>
       </c>
       <c r="N62">
-        <v>-169.704032</v>
+        <v>-174.3690992</v>
       </c>
       <c r="O62">
-        <v>-42.42600800000001</v>
+        <v>-43.5922748</v>
       </c>
       <c r="P62">
-        <v>-127.278024</v>
+        <v>-130.7768244</v>
       </c>
       <c r="Q62">
-        <v>-119.578024</v>
+        <v>-123.0768244</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1958188162338738</v>
+        <v>0.1996654525475629</v>
       </c>
       <c r="T62">
-        <v>3.006926142778703</v>
+        <v>3.084026813106362</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09842659215427092</v>
+        <v>0.09681304146321731</v>
       </c>
       <c r="W62">
-        <v>0.2125910095700229</v>
+        <v>0.2129714848229734</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3937063686170836</v>
+        <v>0.3872521658528693</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2077821322355633</v>
+        <v>0.2096821322355633</v>
       </c>
       <c r="C63">
-        <v>-427.6621033680156</v>
+        <v>-456.4415599409249</v>
       </c>
       <c r="D63">
-        <v>775.8918966319843</v>
+        <v>766.8964400590751</v>
       </c>
       <c r="E63">
-        <v>1187.724</v>
+        <v>1207.508</v>
       </c>
       <c r="F63">
-        <v>1206.824</v>
+        <v>1226.608</v>
       </c>
       <c r="G63">
         <v>3.27</v>
@@ -6563,37 +6563,37 @@
         <v>110.2</v>
       </c>
       <c r="M63">
-        <v>284.5690992</v>
+        <v>289.2341664</v>
       </c>
       <c r="N63">
-        <v>-174.3690992</v>
+        <v>-179.0341664</v>
       </c>
       <c r="O63">
-        <v>-43.5922748</v>
+        <v>-44.7585416</v>
       </c>
       <c r="P63">
-        <v>-130.7768244</v>
+        <v>-134.2756248</v>
       </c>
       <c r="Q63">
-        <v>-123.0768244</v>
+        <v>-126.5756248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1996654525475629</v>
+        <v>0.2037145434040777</v>
       </c>
       <c r="T63">
-        <v>3.084026813106362</v>
+        <v>3.165185413451266</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09681304146321731</v>
+        <v>0.09525154079445575</v>
       </c>
       <c r="W63">
-        <v>0.2129714848229734</v>
+        <v>0.2133396866806674</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3872521658528693</v>
+        <v>0.381006163177823</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6609,22 +6609,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2096821322355633</v>
+        <v>0.2115821322355633</v>
       </c>
       <c r="C64">
-        <v>-456.4415599409249</v>
+        <v>-485.0148258072957</v>
       </c>
       <c r="D64">
-        <v>766.8964400590751</v>
+        <v>758.1071741927042</v>
       </c>
       <c r="E64">
-        <v>1207.508</v>
+        <v>1227.292</v>
       </c>
       <c r="F64">
-        <v>1226.608</v>
+        <v>1246.392</v>
       </c>
       <c r="G64">
         <v>3.27</v>
@@ -6645,37 +6645,37 @@
         <v>110.2</v>
       </c>
       <c r="M64">
-        <v>289.2341664</v>
+        <v>293.8992335999999</v>
       </c>
       <c r="N64">
-        <v>-179.0341664</v>
+        <v>-183.6992336</v>
       </c>
       <c r="O64">
-        <v>-44.7585416</v>
+        <v>-45.92480839999999</v>
       </c>
       <c r="P64">
-        <v>-134.2756248</v>
+        <v>-137.7744252</v>
       </c>
       <c r="Q64">
-        <v>-126.5756248</v>
+        <v>-130.0744252</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2037145434040777</v>
+        <v>0.2079825040366204</v>
       </c>
       <c r="T64">
-        <v>3.165185413451266</v>
+        <v>3.250730965166165</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09525154079445575</v>
+        <v>0.09373961157549615</v>
       </c>
       <c r="W64">
-        <v>0.2133396866806674</v>
+        <v>0.213696199590498</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.381006163177823</v>
+        <v>0.3749584463019845</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6691,22 +6691,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2115821322355633</v>
+        <v>0.2134821322355633</v>
       </c>
       <c r="C65">
-        <v>-485.0148258072957</v>
+        <v>-513.3889099847956</v>
       </c>
       <c r="D65">
-        <v>758.1071741927042</v>
+        <v>749.5170900152043</v>
       </c>
       <c r="E65">
-        <v>1227.292</v>
+        <v>1247.076</v>
       </c>
       <c r="F65">
-        <v>1246.392</v>
+        <v>1266.176</v>
       </c>
       <c r="G65">
         <v>3.27</v>
@@ -6727,37 +6727,37 @@
         <v>110.2</v>
       </c>
       <c r="M65">
-        <v>293.8992335999999</v>
+        <v>298.5643008</v>
       </c>
       <c r="N65">
-        <v>-183.6992336</v>
+        <v>-188.3643008</v>
       </c>
       <c r="O65">
-        <v>-45.92480839999999</v>
+        <v>-47.09107520000001</v>
       </c>
       <c r="P65">
-        <v>-137.7744252</v>
+        <v>-141.2732256</v>
       </c>
       <c r="Q65">
-        <v>-130.0744252</v>
+        <v>-133.5732256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2079825040366204</v>
+        <v>0.2124875735931932</v>
       </c>
       <c r="T65">
-        <v>3.250730965166165</v>
+        <v>3.341029047531892</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09373961157549615</v>
+        <v>0.09227493014462899</v>
       </c>
       <c r="W65">
-        <v>0.213696199590498</v>
+        <v>0.2140415714718965</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3749584463019845</v>
+        <v>0.3690997205785159</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2134821322355633</v>
+        <v>0.2153821322355633</v>
       </c>
       <c r="C66">
-        <v>-513.3889099847956</v>
+        <v>-541.5705073746595</v>
       </c>
       <c r="D66">
-        <v>749.5170900152043</v>
+        <v>741.1194926253405</v>
       </c>
       <c r="E66">
-        <v>1247.076</v>
+        <v>1266.86</v>
       </c>
       <c r="F66">
-        <v>1266.176</v>
+        <v>1285.96</v>
       </c>
       <c r="G66">
         <v>3.27</v>
@@ -6809,37 +6809,37 @@
         <v>110.2</v>
       </c>
       <c r="M66">
-        <v>298.5643008</v>
+        <v>303.229368</v>
       </c>
       <c r="N66">
-        <v>-188.3643008</v>
+        <v>-193.029368</v>
       </c>
       <c r="O66">
-        <v>-47.09107520000001</v>
+        <v>-48.25734200000001</v>
       </c>
       <c r="P66">
-        <v>-141.2732256</v>
+        <v>-144.772026</v>
       </c>
       <c r="Q66">
-        <v>-133.5732256</v>
+        <v>-137.0720260000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2124875735931932</v>
+        <v>0.2172500756958559</v>
       </c>
       <c r="T66">
-        <v>3.341029047531892</v>
+        <v>3.436487020318518</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09227493014462899</v>
+        <v>0.09085531583471163</v>
       </c>
       <c r="W66">
-        <v>0.2140415714718965</v>
+        <v>0.214376316526175</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3690997205785159</v>
+        <v>0.3634212633388465</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6855,22 +6855,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2153821322355633</v>
+        <v>0.2172821322355633</v>
       </c>
       <c r="C67">
-        <v>-541.5705073746595</v>
+        <v>-569.566016163539</v>
       </c>
       <c r="D67">
-        <v>741.1194926253405</v>
+        <v>732.907983836461</v>
       </c>
       <c r="E67">
-        <v>1266.86</v>
+        <v>1286.644</v>
       </c>
       <c r="F67">
-        <v>1285.96</v>
+        <v>1305.744</v>
       </c>
       <c r="G67">
         <v>3.27</v>
@@ -6891,37 +6891,37 @@
         <v>110.2</v>
       </c>
       <c r="M67">
-        <v>303.229368</v>
+        <v>307.8944352</v>
       </c>
       <c r="N67">
-        <v>-193.029368</v>
+        <v>-197.6944352</v>
       </c>
       <c r="O67">
-        <v>-48.25734200000001</v>
+        <v>-49.4236088</v>
       </c>
       <c r="P67">
-        <v>-144.772026</v>
+        <v>-148.2708264</v>
       </c>
       <c r="Q67">
-        <v>-137.0720260000001</v>
+        <v>-140.5708264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2172500756958559</v>
+        <v>0.2222927249810281</v>
       </c>
       <c r="T67">
-        <v>3.436487020318518</v>
+        <v>3.537560167974946</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09085531583471163</v>
+        <v>0.08947872014024631</v>
       </c>
       <c r="W67">
-        <v>0.214376316526175</v>
+        <v>0.21470091779093</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3634212633388465</v>
+        <v>0.3579148805609852</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2172821322355633</v>
+        <v>0.2191821322355633</v>
       </c>
       <c r="C68">
-        <v>-569.566016163539</v>
+        <v>-597.3815540811681</v>
       </c>
       <c r="D68">
-        <v>732.907983836461</v>
+        <v>724.8764459188319</v>
       </c>
       <c r="E68">
-        <v>1286.644</v>
+        <v>1306.428</v>
       </c>
       <c r="F68">
-        <v>1305.744</v>
+        <v>1325.528</v>
       </c>
       <c r="G68">
         <v>3.27</v>
@@ -6973,37 +6973,37 @@
         <v>110.2</v>
       </c>
       <c r="M68">
-        <v>307.8944352</v>
+        <v>312.5595024</v>
       </c>
       <c r="N68">
-        <v>-197.6944352</v>
+        <v>-202.3595024000001</v>
       </c>
       <c r="O68">
-        <v>-49.4236088</v>
+        <v>-50.58987560000001</v>
       </c>
       <c r="P68">
-        <v>-148.2708264</v>
+        <v>-151.7696268</v>
       </c>
       <c r="Q68">
-        <v>-140.5708264</v>
+        <v>-144.0696268</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2222927249810281</v>
+        <v>0.2276409893743926</v>
       </c>
       <c r="T68">
-        <v>3.537560167974946</v>
+        <v>3.644758960943883</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08947872014024631</v>
+        <v>0.08814321685457098</v>
       </c>
       <c r="W68">
-        <v>0.21470091779093</v>
+        <v>0.2150158294656922</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3579148805609852</v>
+        <v>0.3525728674182839</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7019,22 +7019,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2191821322355633</v>
+        <v>0.2210821322355633</v>
       </c>
       <c r="C69">
-        <v>-597.3815540811681</v>
+        <v>-625.0229736006592</v>
       </c>
       <c r="D69">
-        <v>724.8764459188319</v>
+        <v>717.0190263993408</v>
       </c>
       <c r="E69">
-        <v>1306.428</v>
+        <v>1326.212</v>
       </c>
       <c r="F69">
-        <v>1325.528</v>
+        <v>1345.312</v>
       </c>
       <c r="G69">
         <v>3.27</v>
@@ -7055,37 +7055,37 @@
         <v>110.2</v>
       </c>
       <c r="M69">
-        <v>312.5595024</v>
+        <v>317.2245696</v>
       </c>
       <c r="N69">
-        <v>-202.3595024000001</v>
+        <v>-207.0245696</v>
       </c>
       <c r="O69">
-        <v>-50.58987560000001</v>
+        <v>-51.7561424</v>
       </c>
       <c r="P69">
-        <v>-151.7696268</v>
+        <v>-155.2684272</v>
       </c>
       <c r="Q69">
-        <v>-144.0696268</v>
+        <v>-147.5684272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2276409893743926</v>
+        <v>0.2333235202923424</v>
       </c>
       <c r="T69">
-        <v>3.644758960943883</v>
+        <v>3.758657678473379</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08814321685457098</v>
+        <v>0.08684699307729789</v>
       </c>
       <c r="W69">
-        <v>0.2150158294656922</v>
+        <v>0.2153214790323732</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3525728674182839</v>
+        <v>0.3473879723091915</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7101,22 +7101,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2210821322355633</v>
+        <v>0.2229821322355633</v>
       </c>
       <c r="C70">
-        <v>-625.0229736006592</v>
+        <v>-652.4958761608087</v>
       </c>
       <c r="D70">
-        <v>717.0190263993408</v>
+        <v>709.3301238391913</v>
       </c>
       <c r="E70">
-        <v>1326.212</v>
+        <v>1345.996</v>
       </c>
       <c r="F70">
-        <v>1345.312</v>
+        <v>1365.096</v>
       </c>
       <c r="G70">
         <v>3.27</v>
@@ -7137,37 +7137,37 @@
         <v>110.2</v>
       </c>
       <c r="M70">
-        <v>317.2245696</v>
+        <v>321.8896368</v>
       </c>
       <c r="N70">
-        <v>-207.0245696</v>
+        <v>-211.6896368</v>
       </c>
       <c r="O70">
-        <v>-51.7561424</v>
+        <v>-52.9224092</v>
       </c>
       <c r="P70">
-        <v>-155.2684272</v>
+        <v>-158.7672276</v>
       </c>
       <c r="Q70">
-        <v>-147.5684272</v>
+        <v>-151.0672276</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2333235202923424</v>
+        <v>0.2393726661082244</v>
       </c>
       <c r="T70">
-        <v>3.758657678473379</v>
+        <v>3.879904700359618</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08684699307729789</v>
+        <v>0.08558834100371386</v>
       </c>
       <c r="W70">
-        <v>0.2153214790323732</v>
+        <v>0.2156182691913243</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3473879723091915</v>
+        <v>0.3423533640148554</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7183,22 +7183,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2229821322355633</v>
+        <v>0.2248821322355633</v>
       </c>
       <c r="C71">
-        <v>-652.4958761608087</v>
+        <v>-679.8056254830341</v>
       </c>
       <c r="D71">
-        <v>709.3301238391913</v>
+        <v>701.804374516966</v>
       </c>
       <c r="E71">
-        <v>1345.996</v>
+        <v>1365.78</v>
       </c>
       <c r="F71">
-        <v>1365.096</v>
+        <v>1384.88</v>
       </c>
       <c r="G71">
         <v>3.27</v>
@@ -7219,37 +7219,37 @@
         <v>110.2</v>
       </c>
       <c r="M71">
-        <v>321.8896368</v>
+        <v>326.554704</v>
       </c>
       <c r="N71">
-        <v>-211.6896368</v>
+        <v>-216.354704</v>
       </c>
       <c r="O71">
-        <v>-52.9224092</v>
+        <v>-54.08867600000001</v>
       </c>
       <c r="P71">
-        <v>-158.7672276</v>
+        <v>-162.266028</v>
       </c>
       <c r="Q71">
-        <v>-151.0672276</v>
+        <v>-154.566028</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2393726661082244</v>
+        <v>0.2458250883118318</v>
       </c>
       <c r="T71">
-        <v>3.879904700359618</v>
+        <v>4.009234857038271</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08558834100371386</v>
+        <v>0.08436565041794651</v>
       </c>
       <c r="W71">
-        <v>0.2156182691913243</v>
+        <v>0.2159065796314482</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3423533640148554</v>
+        <v>0.337462601671786</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7265,22 +7265,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2248821322355633</v>
+        <v>0.2267821322355633</v>
       </c>
       <c r="C72">
-        <v>-679.8056254830341</v>
+        <v>-706.9573600494865</v>
       </c>
       <c r="D72">
-        <v>701.804374516966</v>
+        <v>694.4366399505135</v>
       </c>
       <c r="E72">
-        <v>1365.78</v>
+        <v>1385.564</v>
       </c>
       <c r="F72">
-        <v>1384.88</v>
+        <v>1404.664</v>
       </c>
       <c r="G72">
         <v>3.27</v>
@@ -7301,37 +7301,37 @@
         <v>110.2</v>
       </c>
       <c r="M72">
-        <v>326.554704</v>
+        <v>331.2197712</v>
       </c>
       <c r="N72">
-        <v>-216.354704</v>
+        <v>-221.0197712</v>
       </c>
       <c r="O72">
-        <v>-54.08867600000001</v>
+        <v>-55.25494280000001</v>
       </c>
       <c r="P72">
-        <v>-162.266028</v>
+        <v>-165.7648284</v>
       </c>
       <c r="Q72">
-        <v>-154.566028</v>
+        <v>-158.0648284</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2458250883118318</v>
+        <v>0.2527225051501709</v>
       </c>
       <c r="T72">
-        <v>4.009234857038271</v>
+        <v>4.147484334867178</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08436565041794651</v>
+        <v>0.08317740182051064</v>
       </c>
       <c r="W72">
-        <v>0.2159065796314482</v>
+        <v>0.2161867686507236</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.337462601671786</v>
+        <v>0.3327096072820426</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7347,22 +7347,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2267821322355633</v>
+        <v>0.2286821322355633</v>
       </c>
       <c r="C73">
-        <v>-706.9573600494861</v>
+        <v>-733.9560048033351</v>
       </c>
       <c r="D73">
-        <v>694.4366399505137</v>
+        <v>687.2219951966648</v>
       </c>
       <c r="E73">
-        <v>1385.564</v>
+        <v>1405.348</v>
       </c>
       <c r="F73">
-        <v>1404.664</v>
+        <v>1424.448</v>
       </c>
       <c r="G73">
         <v>3.27</v>
@@ -7383,37 +7383,37 @@
         <v>110.2</v>
       </c>
       <c r="M73">
-        <v>331.2197712</v>
+        <v>335.8848384</v>
       </c>
       <c r="N73">
-        <v>-221.0197712</v>
+        <v>-225.6848384</v>
       </c>
       <c r="O73">
-        <v>-55.25494279999999</v>
+        <v>-56.4212096</v>
       </c>
       <c r="P73">
-        <v>-165.7648284</v>
+        <v>-169.2636288</v>
       </c>
       <c r="Q73">
-        <v>-158.0648284</v>
+        <v>-161.5636288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2527225051501708</v>
+        <v>0.2601125946198198</v>
       </c>
       <c r="T73">
-        <v>4.147484334867176</v>
+        <v>4.295608775398147</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08317740182051066</v>
+        <v>0.08202216012855912</v>
       </c>
       <c r="W73">
-        <v>0.2161867686507236</v>
+        <v>0.2164591746416858</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3327096072820426</v>
+        <v>0.3280886405142365</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7429,22 +7429,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2286821322355633</v>
+        <v>0.2305821322355633</v>
       </c>
       <c r="C74">
-        <v>-733.9560048033351</v>
+        <v>-760.8062821272113</v>
       </c>
       <c r="D74">
-        <v>687.2219951966648</v>
+        <v>680.1557178727887</v>
       </c>
       <c r="E74">
-        <v>1405.348</v>
+        <v>1425.132</v>
       </c>
       <c r="F74">
-        <v>1424.448</v>
+        <v>1444.232</v>
       </c>
       <c r="G74">
         <v>3.27</v>
@@ -7465,37 +7465,37 @@
         <v>110.2</v>
       </c>
       <c r="M74">
-        <v>335.8848384</v>
+        <v>340.5499056</v>
       </c>
       <c r="N74">
-        <v>-225.6848384</v>
+        <v>-230.3499056</v>
       </c>
       <c r="O74">
-        <v>-56.4212096</v>
+        <v>-57.5874764</v>
       </c>
       <c r="P74">
-        <v>-169.2636288</v>
+        <v>-172.7624292</v>
       </c>
       <c r="Q74">
-        <v>-161.5636288</v>
+        <v>-165.0624292</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2601125946198198</v>
+        <v>0.2680500981242575</v>
       </c>
       <c r="T74">
-        <v>4.295608775398147</v>
+        <v>4.454705396709189</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08202216012855912</v>
+        <v>0.08089856889392132</v>
       </c>
       <c r="W74">
-        <v>0.2164591746416858</v>
+        <v>0.2167241174548133</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3280886405142365</v>
+        <v>0.3235942755756852</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2305821322355633</v>
+        <v>0.2324821322355633</v>
       </c>
       <c r="C75">
-        <v>-760.8062821272113</v>
+        <v>-787.5127221512391</v>
       </c>
       <c r="D75">
-        <v>680.1557178727887</v>
+        <v>673.2332778487607</v>
       </c>
       <c r="E75">
-        <v>1425.132</v>
+        <v>1444.916</v>
       </c>
       <c r="F75">
-        <v>1444.232</v>
+        <v>1464.016</v>
       </c>
       <c r="G75">
         <v>3.27</v>
@@ -7547,37 +7547,37 @@
         <v>110.2</v>
       </c>
       <c r="M75">
-        <v>340.5499056</v>
+        <v>345.2149728</v>
       </c>
       <c r="N75">
-        <v>-230.3499056</v>
+        <v>-235.0149728</v>
       </c>
       <c r="O75">
-        <v>-57.5874764</v>
+        <v>-58.7537432</v>
       </c>
       <c r="P75">
-        <v>-172.7624292</v>
+        <v>-176.2612296</v>
       </c>
       <c r="Q75">
-        <v>-165.0624292</v>
+        <v>-168.5612296</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2680500981242575</v>
+        <v>0.2765981788213444</v>
       </c>
       <c r="T75">
-        <v>4.454705396709189</v>
+        <v>4.626040219659543</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08089856889392132</v>
+        <v>0.0798053449899494</v>
       </c>
       <c r="W75">
-        <v>0.2167241174548133</v>
+        <v>0.2169818996513699</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3235942755756852</v>
+        <v>0.3192213799597976</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7593,22 +7593,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2324821322355633</v>
+        <v>0.2343821322355633</v>
       </c>
       <c r="C76">
-        <v>-787.5127221512391</v>
+        <v>-814.0796724379334</v>
       </c>
       <c r="D76">
-        <v>673.2332778487607</v>
+        <v>666.4503275620666</v>
       </c>
       <c r="E76">
-        <v>1444.916</v>
+        <v>1464.7</v>
       </c>
       <c r="F76">
-        <v>1464.016</v>
+        <v>1483.8</v>
       </c>
       <c r="G76">
         <v>3.27</v>
@@ -7629,37 +7629,37 @@
         <v>110.2</v>
       </c>
       <c r="M76">
-        <v>345.2149728</v>
+        <v>349.88004</v>
       </c>
       <c r="N76">
-        <v>-235.0149728</v>
+        <v>-239.68004</v>
       </c>
       <c r="O76">
-        <v>-58.7537432</v>
+        <v>-59.92001</v>
       </c>
       <c r="P76">
-        <v>-176.2612296</v>
+        <v>-179.76003</v>
       </c>
       <c r="Q76">
-        <v>-168.5612296</v>
+        <v>-172.06003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2765981788213444</v>
+        <v>0.2858301059741982</v>
       </c>
       <c r="T76">
-        <v>4.626040219659543</v>
+        <v>4.811081828445925</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0798053449899494</v>
+        <v>0.07874127372341674</v>
       </c>
       <c r="W76">
-        <v>0.2169818996513699</v>
+        <v>0.2172328076560183</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3192213799597976</v>
+        <v>0.314965094893667</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7675,22 +7675,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2343821322355633</v>
+        <v>0.2362821322355633</v>
       </c>
       <c r="C77">
-        <v>-814.0796724379334</v>
+        <v>-840.5113070874763</v>
       </c>
       <c r="D77">
-        <v>666.4503275620666</v>
+        <v>659.8026929125235</v>
       </c>
       <c r="E77">
-        <v>1464.7</v>
+        <v>1484.484</v>
       </c>
       <c r="F77">
-        <v>1483.8</v>
+        <v>1503.584</v>
       </c>
       <c r="G77">
         <v>3.27</v>
@@ -7711,37 +7711,37 @@
         <v>110.2</v>
       </c>
       <c r="M77">
-        <v>349.88004</v>
+        <v>354.5451072</v>
       </c>
       <c r="N77">
-        <v>-239.68004</v>
+        <v>-244.3451072</v>
       </c>
       <c r="O77">
-        <v>-59.92001</v>
+        <v>-61.08627679999999</v>
       </c>
       <c r="P77">
-        <v>-179.76003</v>
+        <v>-183.2588304</v>
       </c>
       <c r="Q77">
-        <v>-172.06003</v>
+        <v>-175.5588304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2858301059741982</v>
+        <v>0.2958313603897898</v>
       </c>
       <c r="T77">
-        <v>4.811081828445925</v>
+        <v>5.011543571297839</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07874127372341674</v>
+        <v>0.07770520433231917</v>
       </c>
       <c r="W77">
-        <v>0.2172328076560183</v>
+        <v>0.2174771128184391</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.314965094893667</v>
+        <v>0.3108208173292766</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7757,22 +7757,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2362821322355633</v>
+        <v>0.2381821322355633</v>
       </c>
       <c r="C78">
-        <v>-840.5113070874763</v>
+        <v>-866.8116353034396</v>
       </c>
       <c r="D78">
-        <v>659.8026929125235</v>
+        <v>653.2863646965603</v>
       </c>
       <c r="E78">
-        <v>1484.484</v>
+        <v>1504.268</v>
       </c>
       <c r="F78">
-        <v>1503.584</v>
+        <v>1523.368</v>
       </c>
       <c r="G78">
         <v>3.27</v>
@@ -7793,37 +7793,37 @@
         <v>110.2</v>
       </c>
       <c r="M78">
-        <v>354.5451072</v>
+        <v>359.2101744</v>
       </c>
       <c r="N78">
-        <v>-244.3451072</v>
+        <v>-249.0101744</v>
       </c>
       <c r="O78">
-        <v>-61.08627679999999</v>
+        <v>-62.25254360000001</v>
       </c>
       <c r="P78">
-        <v>-183.2588304</v>
+        <v>-186.7576308</v>
       </c>
       <c r="Q78">
-        <v>-175.5588304</v>
+        <v>-179.0576308</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2958313603897898</v>
+        <v>0.3067022891023893</v>
       </c>
       <c r="T78">
-        <v>5.011543571297839</v>
+        <v>5.229436770049919</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07770520433231917</v>
+        <v>0.07669604583449682</v>
       </c>
       <c r="W78">
-        <v>0.2174771128184391</v>
+        <v>0.2177150723922257</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3108208173292766</v>
+        <v>0.3067841833379873</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7839,22 +7839,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2381821322355633</v>
+        <v>0.2400821322355633</v>
       </c>
       <c r="C79">
-        <v>-866.8116353034396</v>
+        <v>-892.984509455894</v>
       </c>
       <c r="D79">
-        <v>653.2863646965603</v>
+        <v>646.8974905441061</v>
       </c>
       <c r="E79">
-        <v>1504.268</v>
+        <v>1524.052</v>
       </c>
       <c r="F79">
-        <v>1523.368</v>
+        <v>1543.152</v>
       </c>
       <c r="G79">
         <v>3.27</v>
@@ -7875,37 +7875,37 @@
         <v>110.2</v>
       </c>
       <c r="M79">
-        <v>359.2101744</v>
+        <v>363.8752416</v>
       </c>
       <c r="N79">
-        <v>-249.0101744</v>
+        <v>-253.6752416</v>
       </c>
       <c r="O79">
-        <v>-62.25254360000001</v>
+        <v>-63.41881040000001</v>
       </c>
       <c r="P79">
-        <v>-186.7576308</v>
+        <v>-190.2564312</v>
       </c>
       <c r="Q79">
-        <v>-179.0576308</v>
+        <v>-182.5564312</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3067022891023893</v>
+        <v>0.3185614840615888</v>
       </c>
       <c r="T79">
-        <v>5.229436770049919</v>
+        <v>5.467138441415823</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07669604583449682</v>
+        <v>0.07571276319559302</v>
       </c>
       <c r="W79">
-        <v>0.2177150723922257</v>
+        <v>0.2179469304384792</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3067841833379873</v>
+        <v>0.302851052782372</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2400821322355633</v>
+        <v>0.2419821322355633</v>
       </c>
       <c r="C80">
-        <v>-892.984509455894</v>
+        <v>-919.0336326759736</v>
       </c>
       <c r="D80">
-        <v>646.8974905441061</v>
+        <v>640.6323673240263</v>
       </c>
       <c r="E80">
-        <v>1524.052</v>
+        <v>1543.836</v>
       </c>
       <c r="F80">
-        <v>1543.152</v>
+        <v>1562.936</v>
       </c>
       <c r="G80">
         <v>3.27</v>
@@ -7957,37 +7957,37 @@
         <v>110.2</v>
       </c>
       <c r="M80">
-        <v>363.8752416</v>
+        <v>368.5403088</v>
       </c>
       <c r="N80">
-        <v>-253.6752416</v>
+        <v>-258.3403088</v>
       </c>
       <c r="O80">
-        <v>-63.41881040000001</v>
+        <v>-64.5850772</v>
       </c>
       <c r="P80">
-        <v>-190.2564312</v>
+        <v>-193.7552316</v>
       </c>
       <c r="Q80">
-        <v>-182.5564312</v>
+        <v>-186.0552316</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3185614840615888</v>
+        <v>0.3315501261597598</v>
       </c>
       <c r="T80">
-        <v>5.467138441415823</v>
+        <v>5.727478367197532</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07571276319559302</v>
+        <v>0.07475437378805387</v>
       </c>
       <c r="W80">
-        <v>0.2179469304384792</v>
+        <v>0.2181729186607769</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.302851052782372</v>
+        <v>0.2990174951522154</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2419821322355633</v>
+        <v>0.2438821322355633</v>
       </c>
       <c r="C81">
-        <v>-919.0336326759736</v>
+        <v>-944.9625660133638</v>
       </c>
       <c r="D81">
-        <v>640.6323673240263</v>
+        <v>634.4874339866362</v>
       </c>
       <c r="E81">
-        <v>1543.836</v>
+        <v>1563.62</v>
       </c>
       <c r="F81">
-        <v>1562.936</v>
+        <v>1582.72</v>
       </c>
       <c r="G81">
         <v>3.27</v>
@@ -8039,37 +8039,37 @@
         <v>110.2</v>
       </c>
       <c r="M81">
-        <v>368.5403088</v>
+        <v>373.205376</v>
       </c>
       <c r="N81">
-        <v>-258.3403088</v>
+        <v>-263.005376</v>
       </c>
       <c r="O81">
-        <v>-64.5850772</v>
+        <v>-65.751344</v>
       </c>
       <c r="P81">
-        <v>-193.7552316</v>
+        <v>-197.254032</v>
       </c>
       <c r="Q81">
-        <v>-186.0552316</v>
+        <v>-189.554032</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3315501261597598</v>
+        <v>0.3458376324677477</v>
       </c>
       <c r="T81">
-        <v>5.727478367197532</v>
+        <v>6.013852285557407</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07475437378805387</v>
+        <v>0.0738199441157032</v>
       </c>
       <c r="W81">
-        <v>0.2181729186607769</v>
+        <v>0.2183932571775172</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2990174951522154</v>
+        <v>0.2952797764628128</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8085,22 +8085,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2438821322355633</v>
+        <v>0.2457821322355633</v>
       </c>
       <c r="C82">
-        <v>-944.9625660133638</v>
+        <v>-970.7747351857706</v>
       </c>
       <c r="D82">
-        <v>634.4874339866362</v>
+        <v>628.4592648142293</v>
       </c>
       <c r="E82">
-        <v>1563.62</v>
+        <v>1583.404</v>
       </c>
       <c r="F82">
-        <v>1582.72</v>
+        <v>1602.504</v>
       </c>
       <c r="G82">
         <v>3.27</v>
@@ -8121,37 +8121,37 @@
         <v>110.2</v>
       </c>
       <c r="M82">
-        <v>373.205376</v>
+        <v>377.8704432</v>
       </c>
       <c r="N82">
-        <v>-263.005376</v>
+        <v>-267.6704432</v>
       </c>
       <c r="O82">
-        <v>-65.751344</v>
+        <v>-66.91761080000001</v>
       </c>
       <c r="P82">
-        <v>-197.254032</v>
+        <v>-200.7528324</v>
       </c>
       <c r="Q82">
-        <v>-189.554032</v>
+        <v>-193.0528324</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3458376324677477</v>
+        <v>0.3616290868081556</v>
       </c>
       <c r="T82">
-        <v>6.013852285557407</v>
+        <v>6.330370826902534</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0738199441157032</v>
+        <v>0.07290858678094143</v>
       </c>
       <c r="W82">
-        <v>0.2183932571775172</v>
+        <v>0.218608155237054</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2952797764628128</v>
+        <v>0.2916343471237657</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8167,22 +8167,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2457821322355633</v>
+        <v>0.2476821322355633</v>
       </c>
       <c r="C83">
-        <v>-970.7747351857706</v>
+        <v>-996.4734369472607</v>
       </c>
       <c r="D83">
-        <v>628.4592648142293</v>
+        <v>622.5445630527394</v>
       </c>
       <c r="E83">
-        <v>1583.404</v>
+        <v>1603.188</v>
       </c>
       <c r="F83">
-        <v>1602.504</v>
+        <v>1622.288</v>
       </c>
       <c r="G83">
         <v>3.27</v>
@@ -8203,37 +8203,37 @@
         <v>110.2</v>
       </c>
       <c r="M83">
-        <v>377.8704432</v>
+        <v>382.5355104</v>
       </c>
       <c r="N83">
-        <v>-267.6704432</v>
+        <v>-272.3355104</v>
       </c>
       <c r="O83">
-        <v>-66.91761080000001</v>
+        <v>-68.08387760000001</v>
       </c>
       <c r="P83">
-        <v>-200.7528324</v>
+        <v>-204.2516328</v>
       </c>
       <c r="Q83">
-        <v>-193.0528324</v>
+        <v>-196.5516328</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3616290868081556</v>
+        <v>0.3791751471863865</v>
       </c>
       <c r="T83">
-        <v>6.330370826902534</v>
+        <v>6.682058095063787</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07290858678094143</v>
+        <v>0.07201945767385677</v>
       </c>
       <c r="W83">
-        <v>0.218608155237054</v>
+        <v>0.2188178118805046</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2916343471237657</v>
+        <v>0.288077830695427</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8249,22 +8249,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2476821322355633</v>
+        <v>0.2495821322355633</v>
       </c>
       <c r="C84">
-        <v>-996.4734369472607</v>
+        <v>-1022.061845100341</v>
       </c>
       <c r="D84">
-        <v>622.5445630527394</v>
+        <v>616.740154899659</v>
       </c>
       <c r="E84">
-        <v>1603.188</v>
+        <v>1622.972</v>
       </c>
       <c r="F84">
-        <v>1622.288</v>
+        <v>1642.072</v>
       </c>
       <c r="G84">
         <v>3.27</v>
@@ -8285,37 +8285,37 @@
         <v>110.2</v>
       </c>
       <c r="M84">
-        <v>382.5355104</v>
+        <v>387.2005776</v>
       </c>
       <c r="N84">
-        <v>-272.3355104</v>
+        <v>-277.0005776</v>
       </c>
       <c r="O84">
-        <v>-68.08387760000001</v>
+        <v>-69.25014440000001</v>
       </c>
       <c r="P84">
-        <v>-204.2516328</v>
+        <v>-207.7504332</v>
       </c>
       <c r="Q84">
-        <v>-196.5516328</v>
+        <v>-200.0504332</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3791751471863865</v>
+        <v>0.3987854499620563</v>
       </c>
       <c r="T84">
-        <v>6.682058095063787</v>
+        <v>7.075120335949892</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07201945767385677</v>
+        <v>0.07115175336453319</v>
       </c>
       <c r="W84">
-        <v>0.2188178118805046</v>
+        <v>0.2190224165566431</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.288077830695427</v>
+        <v>0.2846070134581328</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8331,22 +8331,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2495821322355633</v>
+        <v>0.2514821322355633</v>
       </c>
       <c r="C85">
-        <v>-1022.061845100341</v>
+        <v>-1047.543016174819</v>
       </c>
       <c r="D85">
-        <v>616.740154899659</v>
+        <v>611.0429838251812</v>
       </c>
       <c r="E85">
-        <v>1622.972</v>
+        <v>1642.756</v>
       </c>
       <c r="F85">
-        <v>1642.072</v>
+        <v>1661.856</v>
       </c>
       <c r="G85">
         <v>3.27</v>
@@ -8367,37 +8367,37 @@
         <v>110.2</v>
       </c>
       <c r="M85">
-        <v>387.2005776</v>
+        <v>391.8656448</v>
       </c>
       <c r="N85">
-        <v>-277.0005776</v>
+        <v>-281.6656448000001</v>
       </c>
       <c r="O85">
-        <v>-69.25014440000001</v>
+        <v>-70.41641120000001</v>
       </c>
       <c r="P85">
-        <v>-207.7504332</v>
+        <v>-211.2492336</v>
       </c>
       <c r="Q85">
-        <v>-200.0504332</v>
+        <v>-203.5492336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3987854499620563</v>
+        <v>0.4208470405846849</v>
       </c>
       <c r="T85">
-        <v>7.075120335949892</v>
+        <v>7.517315356946762</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07115175336453319</v>
+        <v>0.07030470868162209</v>
       </c>
       <c r="W85">
-        <v>0.2190224165566431</v>
+        <v>0.2192221496928735</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2846070134581328</v>
+        <v>0.2812188347264883</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8413,22 +8413,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2514821322355633</v>
+        <v>0.2533821322355633</v>
       </c>
       <c r="C86">
-        <v>-1047.543016174818</v>
+        <v>-1072.919894794788</v>
       </c>
       <c r="D86">
-        <v>611.0429838251814</v>
+        <v>605.4501052052124</v>
       </c>
       <c r="E86">
-        <v>1642.756</v>
+        <v>1662.54</v>
       </c>
       <c r="F86">
-        <v>1661.856</v>
+        <v>1681.64</v>
       </c>
       <c r="G86">
         <v>3.27</v>
@@ -8449,37 +8449,37 @@
         <v>110.2</v>
       </c>
       <c r="M86">
-        <v>391.8656448</v>
+        <v>396.530712</v>
       </c>
       <c r="N86">
-        <v>-281.6656448</v>
+        <v>-286.330712</v>
       </c>
       <c r="O86">
-        <v>-70.4164112</v>
+        <v>-71.582678</v>
       </c>
       <c r="P86">
-        <v>-211.2492336</v>
+        <v>-214.748034</v>
       </c>
       <c r="Q86">
-        <v>-203.5492336</v>
+        <v>-207.048034</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4208470405846845</v>
+        <v>0.4458501766236636</v>
       </c>
       <c r="T86">
-        <v>7.517315356946756</v>
+        <v>8.018469714076542</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0703047086816221</v>
+        <v>0.06947759446183831</v>
       </c>
       <c r="W86">
-        <v>0.2192221496928735</v>
+        <v>0.2194171832258985</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2812188347264883</v>
+        <v>0.2779103778473532</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2533821322355633</v>
+        <v>0.2552821322355633</v>
       </c>
       <c r="C87">
-        <v>-1072.919894794788</v>
+        <v>-1098.195318753545</v>
       </c>
       <c r="D87">
-        <v>605.4501052052124</v>
+        <v>599.9586812464552</v>
       </c>
       <c r="E87">
-        <v>1662.54</v>
+        <v>1682.324</v>
       </c>
       <c r="F87">
-        <v>1681.64</v>
+        <v>1701.424</v>
       </c>
       <c r="G87">
         <v>3.27</v>
@@ -8531,37 +8531,37 @@
         <v>110.2</v>
       </c>
       <c r="M87">
-        <v>396.530712</v>
+        <v>401.1957791999999</v>
       </c>
       <c r="N87">
-        <v>-286.330712</v>
+        <v>-290.9957792</v>
       </c>
       <c r="O87">
-        <v>-71.582678</v>
+        <v>-72.74894479999999</v>
       </c>
       <c r="P87">
-        <v>-214.748034</v>
+        <v>-218.2468344</v>
       </c>
       <c r="Q87">
-        <v>-207.048034</v>
+        <v>-210.5468344</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4458501766236636</v>
+        <v>0.4744251892396396</v>
       </c>
       <c r="T87">
-        <v>8.018469714076542</v>
+        <v>8.591217550796294</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06947759446183831</v>
+        <v>0.06866971545646811</v>
       </c>
       <c r="W87">
-        <v>0.2194171832258985</v>
+        <v>0.2196076810953648</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2779103778473532</v>
+        <v>0.2746788618258724</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8577,22 +8577,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2552821322355633</v>
+        <v>0.2571821322355633</v>
       </c>
       <c r="C88">
-        <v>-1098.195318753545</v>
+        <v>-1123.372023814812</v>
       </c>
       <c r="D88">
-        <v>599.9586812464552</v>
+        <v>594.5659761851875</v>
       </c>
       <c r="E88">
-        <v>1682.324</v>
+        <v>1702.108</v>
       </c>
       <c r="F88">
-        <v>1701.424</v>
+        <v>1721.208</v>
       </c>
       <c r="G88">
         <v>3.27</v>
@@ -8613,37 +8613,37 @@
         <v>110.2</v>
       </c>
       <c r="M88">
-        <v>401.1957791999999</v>
+        <v>405.8608464</v>
       </c>
       <c r="N88">
-        <v>-290.9957792</v>
+        <v>-295.6608464</v>
       </c>
       <c r="O88">
-        <v>-72.74894479999999</v>
+        <v>-73.91521159999999</v>
       </c>
       <c r="P88">
-        <v>-218.2468344</v>
+        <v>-221.7456348</v>
       </c>
       <c r="Q88">
-        <v>-210.5468344</v>
+        <v>-214.0456348</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4744251892396396</v>
+        <v>0.5073963576426888</v>
       </c>
       <c r="T88">
-        <v>8.591217550796294</v>
+        <v>9.252080439319085</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06866971545646811</v>
+        <v>0.06788040838225583</v>
       </c>
       <c r="W88">
-        <v>0.2196076810953648</v>
+        <v>0.2197937997034641</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2746788618258724</v>
+        <v>0.2715216335290233</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2571821322355633</v>
+        <v>0.2590821322355633</v>
       </c>
       <c r="C89">
-        <v>-1123.372023814812</v>
+        <v>-1148.452648257334</v>
       </c>
       <c r="D89">
-        <v>594.5659761851875</v>
+        <v>589.2693517426665</v>
       </c>
       <c r="E89">
-        <v>1702.108</v>
+        <v>1721.892</v>
       </c>
       <c r="F89">
-        <v>1721.208</v>
+        <v>1740.992</v>
       </c>
       <c r="G89">
         <v>3.27</v>
@@ -8695,37 +8695,37 @@
         <v>110.2</v>
       </c>
       <c r="M89">
-        <v>405.8608464</v>
+        <v>410.5259136</v>
       </c>
       <c r="N89">
-        <v>-295.6608464</v>
+        <v>-300.3259136</v>
       </c>
       <c r="O89">
-        <v>-73.91521159999999</v>
+        <v>-75.08147840000001</v>
       </c>
       <c r="P89">
-        <v>-221.7456348</v>
+        <v>-225.2444352</v>
       </c>
       <c r="Q89">
-        <v>-214.0456348</v>
+        <v>-217.5444352</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5073963576426888</v>
+        <v>0.5458627207795795</v>
       </c>
       <c r="T89">
-        <v>9.252080439319085</v>
+        <v>10.02308714259568</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06788040838225583</v>
+        <v>0.06710904010518473</v>
       </c>
       <c r="W89">
-        <v>0.2197937997034641</v>
+        <v>0.2199756883431974</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2715216335290233</v>
+        <v>0.2684361604207388</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8741,22 +8741,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2590821322355633</v>
+        <v>0.2609821322355633</v>
       </c>
       <c r="C90">
-        <v>-1148.452648257334</v>
+        <v>-1173.4397371787</v>
       </c>
       <c r="D90">
-        <v>589.2693517426665</v>
+        <v>584.0662628212993</v>
       </c>
       <c r="E90">
-        <v>1721.892</v>
+        <v>1741.676</v>
       </c>
       <c r="F90">
-        <v>1740.992</v>
+        <v>1760.776</v>
       </c>
       <c r="G90">
         <v>3.27</v>
@@ -8777,37 +8777,37 @@
         <v>110.2</v>
       </c>
       <c r="M90">
-        <v>410.5259136</v>
+        <v>415.1909808</v>
       </c>
       <c r="N90">
-        <v>-300.3259136</v>
+        <v>-304.9909808</v>
       </c>
       <c r="O90">
-        <v>-75.08147840000001</v>
+        <v>-76.2477452</v>
       </c>
       <c r="P90">
-        <v>-225.2444352</v>
+        <v>-228.7432356</v>
       </c>
       <c r="Q90">
-        <v>-217.5444352</v>
+        <v>-221.0432356</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5458627207795795</v>
+        <v>0.5913229681231778</v>
       </c>
       <c r="T90">
-        <v>10.02308714259568</v>
+        <v>10.93427688283165</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06710904010518473</v>
+        <v>0.06635500594669951</v>
       </c>
       <c r="W90">
-        <v>0.2199756883431974</v>
+        <v>0.2201534895977683</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2684361604207388</v>
+        <v>0.265420023786798</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8823,22 +8823,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2609821322355633</v>
+        <v>0.2628821322355633</v>
       </c>
       <c r="C91">
-        <v>-1173.4397371787</v>
+        <v>-1198.335746573174</v>
       </c>
       <c r="D91">
-        <v>584.0662628212993</v>
+        <v>578.9542534268261</v>
       </c>
       <c r="E91">
-        <v>1741.676</v>
+        <v>1761.46</v>
       </c>
       <c r="F91">
-        <v>1760.776</v>
+        <v>1780.56</v>
       </c>
       <c r="G91">
         <v>3.27</v>
@@ -8859,37 +8859,37 @@
         <v>110.2</v>
       </c>
       <c r="M91">
-        <v>415.1909808</v>
+        <v>419.856048</v>
       </c>
       <c r="N91">
-        <v>-304.9909808</v>
+        <v>-309.656048</v>
       </c>
       <c r="O91">
-        <v>-76.2477452</v>
+        <v>-77.414012</v>
       </c>
       <c r="P91">
-        <v>-228.7432356</v>
+        <v>-232.242036</v>
       </c>
       <c r="Q91">
-        <v>-221.0432356</v>
+        <v>-224.542036</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5913229681231778</v>
+        <v>0.6458752649354954</v>
       </c>
       <c r="T91">
-        <v>10.93427688283165</v>
+        <v>12.02770457111481</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06635500594669951</v>
+        <v>0.06561772810284729</v>
       </c>
       <c r="W91">
-        <v>0.2201534895977683</v>
+        <v>0.2203273397133486</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.265420023786798</v>
+        <v>0.2624709124113891</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8905,22 +8905,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2628821322355633</v>
+        <v>0.2647821322355633</v>
       </c>
       <c r="C92">
-        <v>-1198.335746573174</v>
+        <v>-1223.143047197207</v>
       </c>
       <c r="D92">
-        <v>578.9542534268261</v>
+        <v>573.9309528027933</v>
       </c>
       <c r="E92">
-        <v>1761.46</v>
+        <v>1781.244</v>
       </c>
       <c r="F92">
-        <v>1780.56</v>
+        <v>1800.344</v>
       </c>
       <c r="G92">
         <v>3.27</v>
@@ -8941,37 +8941,37 @@
         <v>110.2</v>
       </c>
       <c r="M92">
-        <v>419.856048</v>
+        <v>424.5211152000001</v>
       </c>
       <c r="N92">
-        <v>-309.656048</v>
+        <v>-314.3211152000001</v>
       </c>
       <c r="O92">
-        <v>-77.414012</v>
+        <v>-78.58027880000002</v>
       </c>
       <c r="P92">
-        <v>-232.242036</v>
+        <v>-235.7408364</v>
       </c>
       <c r="Q92">
-        <v>-224.542036</v>
+        <v>-228.0408364</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6458752649354954</v>
+        <v>0.7125502943727728</v>
       </c>
       <c r="T92">
-        <v>12.02770457111481</v>
+        <v>13.36411619012757</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06561772810284729</v>
+        <v>0.06489665416765115</v>
       </c>
       <c r="W92">
-        <v>0.2203273397133486</v>
+        <v>0.2204973689472679</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2624709124113891</v>
+        <v>0.2595866166706046</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8987,22 +8987,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2647821322355633</v>
+        <v>0.2666821322355633</v>
       </c>
       <c r="C93">
-        <v>-1223.143047197207</v>
+        <v>-1247.863928235472</v>
       </c>
       <c r="D93">
-        <v>573.9309528027933</v>
+        <v>568.994071764528</v>
       </c>
       <c r="E93">
-        <v>1781.244</v>
+        <v>1801.028</v>
       </c>
       <c r="F93">
-        <v>1800.344</v>
+        <v>1820.128</v>
       </c>
       <c r="G93">
         <v>3.27</v>
@@ -9023,37 +9023,37 @@
         <v>110.2</v>
       </c>
       <c r="M93">
-        <v>424.5211152000001</v>
+        <v>429.1861824</v>
       </c>
       <c r="N93">
-        <v>-314.3211152000001</v>
+        <v>-318.9861824</v>
       </c>
       <c r="O93">
-        <v>-78.58027880000002</v>
+        <v>-79.7465456</v>
       </c>
       <c r="P93">
-        <v>-235.7408364</v>
+        <v>-239.2396368</v>
       </c>
       <c r="Q93">
-        <v>-228.0408364</v>
+        <v>-231.5396368</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7125502943727728</v>
+        <v>0.7958940811693697</v>
       </c>
       <c r="T93">
-        <v>13.36411619012757</v>
+        <v>15.03463071389352</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06489665416765115</v>
+        <v>0.06419125575278539</v>
       </c>
       <c r="W93">
-        <v>0.2204973689472679</v>
+        <v>0.2206637018934932</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2595866166706046</v>
+        <v>0.2567650230111416</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9069,22 +9069,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2666821322355633</v>
+        <v>0.2685821322355633</v>
       </c>
       <c r="C94">
-        <v>-1247.863928235472</v>
+        <v>-1272.500600779289</v>
       </c>
       <c r="D94">
-        <v>568.994071764528</v>
+        <v>564.1413992207108</v>
       </c>
       <c r="E94">
-        <v>1801.028</v>
+        <v>1820.812</v>
       </c>
       <c r="F94">
-        <v>1820.128</v>
+        <v>1839.912</v>
       </c>
       <c r="G94">
         <v>3.27</v>
@@ -9105,37 +9105,37 @@
         <v>110.2</v>
       </c>
       <c r="M94">
-        <v>429.1861824</v>
+        <v>433.8512496</v>
       </c>
       <c r="N94">
-        <v>-318.9861824</v>
+        <v>-323.6512496</v>
       </c>
       <c r="O94">
-        <v>-79.7465456</v>
+        <v>-80.91281240000001</v>
       </c>
       <c r="P94">
-        <v>-239.2396368</v>
+        <v>-242.7384372</v>
       </c>
       <c r="Q94">
-        <v>-231.5396368</v>
+        <v>-235.0384372</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7958940811693697</v>
+        <v>0.9030503784792796</v>
       </c>
       <c r="T94">
-        <v>15.03463071389352</v>
+        <v>17.1824351015926</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06419125575278539</v>
+        <v>0.06350102719630382</v>
       </c>
       <c r="W94">
-        <v>0.2206637018934932</v>
+        <v>0.2208264577871116</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2567650230111416</v>
+        <v>0.2540041087852153</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9151,22 +9151,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2685821322355633</v>
+        <v>0.2704821322355633</v>
       </c>
       <c r="C95">
-        <v>-1272.500600779289</v>
+        <v>-1297.055201128567</v>
       </c>
       <c r="D95">
-        <v>564.1413992207108</v>
+        <v>559.3707988714334</v>
       </c>
       <c r="E95">
-        <v>1820.812</v>
+        <v>1840.596</v>
       </c>
       <c r="F95">
-        <v>1839.912</v>
+        <v>1859.696</v>
       </c>
       <c r="G95">
         <v>3.27</v>
@@ -9187,37 +9187,37 @@
         <v>110.2</v>
       </c>
       <c r="M95">
-        <v>433.8512496</v>
+        <v>438.5163168</v>
       </c>
       <c r="N95">
-        <v>-323.6512496</v>
+        <v>-328.3163168</v>
       </c>
       <c r="O95">
-        <v>-80.91281240000001</v>
+        <v>-82.0790792</v>
       </c>
       <c r="P95">
-        <v>-242.7384372</v>
+        <v>-246.2372376</v>
       </c>
       <c r="Q95">
-        <v>-235.0384372</v>
+        <v>-238.5372376</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9030503784792796</v>
+        <v>1.04592544155916</v>
       </c>
       <c r="T95">
-        <v>17.1824351015926</v>
+        <v>20.04617428519137</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06350102719630382</v>
+        <v>0.06282548435378996</v>
       </c>
       <c r="W95">
-        <v>0.2208264577871116</v>
+        <v>0.2209857507893763</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2540041087852153</v>
+        <v>0.2513019374151598</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9233,22 +9233,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2704821322355633</v>
+        <v>0.2723821322355633</v>
       </c>
       <c r="C96">
-        <v>-1297.055201128567</v>
+        <v>-1321.529793927609</v>
       </c>
       <c r="D96">
-        <v>559.3707988714334</v>
+        <v>554.6802060723912</v>
       </c>
       <c r="E96">
-        <v>1840.596</v>
+        <v>1860.38</v>
       </c>
       <c r="F96">
-        <v>1859.696</v>
+        <v>1879.48</v>
       </c>
       <c r="G96">
         <v>3.27</v>
@@ -9269,37 +9269,37 @@
         <v>110.2</v>
       </c>
       <c r="M96">
-        <v>438.5163168</v>
+        <v>443.181384</v>
       </c>
       <c r="N96">
-        <v>-328.3163168</v>
+        <v>-332.981384</v>
       </c>
       <c r="O96">
-        <v>-82.0790792</v>
+        <v>-83.24534600000001</v>
       </c>
       <c r="P96">
-        <v>-246.2372376</v>
+        <v>-249.736038</v>
       </c>
       <c r="Q96">
-        <v>-238.5372376</v>
+        <v>-242.036038</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.04592544155916</v>
+        <v>1.245950529870993</v>
       </c>
       <c r="T96">
-        <v>20.04617428519137</v>
+        <v>24.05540914222966</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06282548435378996</v>
+        <v>0.06216416346585532</v>
       </c>
       <c r="W96">
-        <v>0.2209857507893763</v>
+        <v>0.2211416902547513</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2513019374151598</v>
+        <v>0.2486566538634213</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9315,22 +9315,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2723821322355633</v>
+        <v>0.2742821322355633</v>
       </c>
       <c r="C97">
-        <v>-1321.529793927609</v>
+        <v>-1345.926375144467</v>
       </c>
       <c r="D97">
-        <v>554.6802060723912</v>
+        <v>550.0676248555328</v>
       </c>
       <c r="E97">
-        <v>1860.38</v>
+        <v>1880.164</v>
       </c>
       <c r="F97">
-        <v>1879.48</v>
+        <v>1899.264</v>
       </c>
       <c r="G97">
         <v>3.27</v>
@@ -9351,37 +9351,37 @@
         <v>110.2</v>
       </c>
       <c r="M97">
-        <v>443.181384</v>
+        <v>447.8464512</v>
       </c>
       <c r="N97">
-        <v>-332.981384</v>
+        <v>-337.6464512000001</v>
       </c>
       <c r="O97">
-        <v>-83.24534600000001</v>
+        <v>-84.41161280000001</v>
       </c>
       <c r="P97">
-        <v>-249.736038</v>
+        <v>-253.2348384000001</v>
       </c>
       <c r="Q97">
-        <v>-242.036038</v>
+        <v>-245.5348384000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.245950529870993</v>
+        <v>1.545988162338741</v>
       </c>
       <c r="T97">
-        <v>24.05540914222966</v>
+        <v>30.06926142778708</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06216416346585532</v>
+        <v>0.06151662009641932</v>
       </c>
       <c r="W97">
-        <v>0.2211416902547513</v>
+        <v>0.2212943809812643</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2486566538634213</v>
+        <v>0.2460664803856772</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2742821322355633</v>
+        <v>0.2761821322355633</v>
       </c>
       <c r="C98">
-        <v>-1345.926375144467</v>
+        <v>-1370.246874902864</v>
       </c>
       <c r="D98">
-        <v>550.0676248555328</v>
+        <v>545.5311250971364</v>
       </c>
       <c r="E98">
-        <v>1880.164</v>
+        <v>1899.948</v>
       </c>
       <c r="F98">
-        <v>1899.264</v>
+        <v>1919.048</v>
       </c>
       <c r="G98">
         <v>3.27</v>
@@ -9433,37 +9433,37 @@
         <v>110.2</v>
       </c>
       <c r="M98">
-        <v>447.8464512</v>
+        <v>452.5115183999999</v>
       </c>
       <c r="N98">
-        <v>-337.6464512</v>
+        <v>-342.3115184</v>
       </c>
       <c r="O98">
-        <v>-84.4116128</v>
+        <v>-85.57787959999999</v>
       </c>
       <c r="P98">
-        <v>-253.2348384</v>
+        <v>-256.7336388</v>
       </c>
       <c r="Q98">
-        <v>-245.5348384</v>
+        <v>-249.0336388</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.545988162338737</v>
+        <v>2.046050883118316</v>
       </c>
       <c r="T98">
-        <v>30.069261427787</v>
+        <v>40.09234857038268</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06151662009641934</v>
+        <v>0.06088242813666244</v>
       </c>
       <c r="W98">
-        <v>0.2212943809812643</v>
+        <v>0.221443923445375</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2460664803856774</v>
+        <v>0.2435297125466498</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9479,22 +9479,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2761821322355633</v>
+        <v>0.2780821322355633</v>
       </c>
       <c r="C99">
-        <v>-1370.246874902864</v>
+        <v>-1394.493160175126</v>
       </c>
       <c r="D99">
-        <v>545.5311250971364</v>
+        <v>541.0688398248735</v>
       </c>
       <c r="E99">
-        <v>1899.948</v>
+        <v>1919.732</v>
       </c>
       <c r="F99">
-        <v>1919.048</v>
+        <v>1938.832</v>
       </c>
       <c r="G99">
         <v>3.27</v>
@@ -9515,37 +9515,37 @@
         <v>110.2</v>
       </c>
       <c r="M99">
-        <v>452.5115183999999</v>
+        <v>457.1765856</v>
       </c>
       <c r="N99">
-        <v>-342.3115184</v>
+        <v>-346.9765856</v>
       </c>
       <c r="O99">
-        <v>-85.57787959999999</v>
+        <v>-86.74414640000001</v>
       </c>
       <c r="P99">
-        <v>-256.7336388</v>
+        <v>-260.2324392</v>
       </c>
       <c r="Q99">
-        <v>-249.0336388</v>
+        <v>-252.5324392000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.046050883118316</v>
+        <v>3.046176324677474</v>
       </c>
       <c r="T99">
-        <v>40.09234857038268</v>
+        <v>60.138522855574</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06088242813666244</v>
+        <v>0.0602611788699618</v>
       </c>
       <c r="W99">
-        <v>0.221443923445375</v>
+        <v>0.221590414022463</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2435297125466498</v>
+        <v>0.2410447154798472</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9561,22 +9561,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2780821322355633</v>
+        <v>0.2799821322355633</v>
       </c>
       <c r="C100">
-        <v>-1394.493160175126</v>
+        <v>-1418.667037344035</v>
       </c>
       <c r="D100">
-        <v>541.0688398248735</v>
+        <v>536.6789626559649</v>
       </c>
       <c r="E100">
-        <v>1919.732</v>
+        <v>1939.516</v>
       </c>
       <c r="F100">
-        <v>1938.832</v>
+        <v>1958.616</v>
       </c>
       <c r="G100">
         <v>3.27</v>
@@ -9597,37 +9597,37 @@
         <v>110.2</v>
       </c>
       <c r="M100">
-        <v>457.1765856</v>
+        <v>461.8416528</v>
       </c>
       <c r="N100">
-        <v>-346.9765856</v>
+        <v>-351.6416528</v>
       </c>
       <c r="O100">
-        <v>-86.74414640000001</v>
+        <v>-87.91041319999999</v>
       </c>
       <c r="P100">
-        <v>-260.2324392</v>
+        <v>-263.7312396</v>
       </c>
       <c r="Q100">
-        <v>-252.5324392000001</v>
+        <v>-256.0312396</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.046176324677474</v>
+        <v>6.046552649354949</v>
       </c>
       <c r="T100">
-        <v>60.138522855574</v>
+        <v>120.277045711148</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0602611788699618</v>
+        <v>0.05965248009349754</v>
       </c>
       <c r="W100">
-        <v>0.221590414022463</v>
+        <v>0.2217339451939533</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9635,91 +9635,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2410447154798472</v>
+        <v>0.2386099203739901</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2799821322355633</v>
-      </c>
-      <c r="C101">
-        <v>-1418.667037344035</v>
-      </c>
-      <c r="D101">
-        <v>536.6789626559649</v>
-      </c>
-      <c r="E101">
-        <v>1939.516</v>
-      </c>
-      <c r="F101">
-        <v>1958.616</v>
-      </c>
-      <c r="G101">
-        <v>3.27</v>
-      </c>
-      <c r="H101">
-        <v>1959.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>117.9</v>
-      </c>
-      <c r="K101">
-        <v>7.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>110.2</v>
-      </c>
-      <c r="M101">
-        <v>461.8416528</v>
-      </c>
-      <c r="N101">
-        <v>-351.6416528</v>
-      </c>
-      <c r="O101">
-        <v>-87.91041319999999</v>
-      </c>
-      <c r="P101">
-        <v>-263.7312396</v>
-      </c>
-      <c r="Q101">
-        <v>-256.0312396</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.046552649354949</v>
-      </c>
-      <c r="T101">
-        <v>120.277045711148</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05965248009349754</v>
-      </c>
-      <c r="W101">
-        <v>0.2217339451939533</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2386099203739901</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
